--- a/cub (1).xlsx
+++ b/cub (1).xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\CUB_LOG - Main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CUB_LOG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EC20BE5-925C-4FE0-9288-517473CC08D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2F5586E-91DF-43EA-9391-837BED56B8D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="45">
   <si>
     <t>8:45 to 9:45</t>
   </si>
@@ -118,55 +118,10 @@
     <t>R.K.Monica</t>
   </si>
   <si>
-    <t xml:space="preserve">BARATH VISHNU J </t>
-  </si>
-  <si>
-    <t>Harrish AR</t>
-  </si>
-  <si>
-    <t>G s sivapriyaa</t>
-  </si>
-  <si>
-    <t>Mahalakshmi M</t>
-  </si>
-  <si>
-    <t>Khailash S</t>
-  </si>
-  <si>
     <t>Shubham Pandey</t>
   </si>
   <si>
-    <t>T Bharath Kumar</t>
-  </si>
-  <si>
-    <t>Kishore S</t>
-  </si>
-  <si>
     <t>Chandresh J</t>
-  </si>
-  <si>
-    <t>Vaitheesh R</t>
-  </si>
-  <si>
-    <t>Calvin Gabriel P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G Balaji Revanth Chowdary </t>
-  </si>
-  <si>
-    <t>Rishi Grace M</t>
-  </si>
-  <si>
-    <t>SELVAKUMARAN B</t>
-  </si>
-  <si>
-    <t>B. Abhishek Perumal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kashi Ramanathan Valliappa </t>
-  </si>
-  <si>
-    <t>Ram Aditya R</t>
   </si>
   <si>
     <t>System occupied</t>
@@ -227,7 +182,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -267,12 +222,6 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos"/>
     </font>
     <font>
       <sz val="12"/>
@@ -330,25 +279,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -415,53 +351,41 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -794,29 +718,29 @@
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4">
-        <v>1</v>
-      </c>
-      <c r="E3" s="4">
-        <v>1</v>
-      </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4">
-        <v>1</v>
-      </c>
-      <c r="H3" s="4">
-        <v>1</v>
-      </c>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="6">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3">
+        <v>1</v>
+      </c>
+      <c r="H3" s="3">
+        <v>1</v>
+      </c>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="5">
         <f t="shared" ref="N3:N33" si="0">SUM(C3:M3)</f>
         <v>4</v>
       </c>
@@ -825,29 +749,29 @@
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4">
-        <v>1</v>
-      </c>
-      <c r="E4" s="4">
-        <v>1</v>
-      </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4">
-        <v>1</v>
-      </c>
-      <c r="H4" s="8">
-        <v>1</v>
-      </c>
-      <c r="I4" s="5"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="6">
+      <c r="C4" s="3"/>
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3">
+        <v>1</v>
+      </c>
+      <c r="H4" s="6">
+        <v>1</v>
+      </c>
+      <c r="I4" s="4"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -856,31 +780,31 @@
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="4">
-        <v>1</v>
-      </c>
-      <c r="E5" s="4">
-        <v>1</v>
-      </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4">
-        <v>1</v>
-      </c>
-      <c r="H5" s="4">
-        <v>1</v>
-      </c>
-      <c r="I5" s="9">
-        <v>1</v>
-      </c>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="6">
+      <c r="C5" s="6"/>
+      <c r="D5" s="3">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3">
+        <v>1</v>
+      </c>
+      <c r="H5" s="3">
+        <v>1</v>
+      </c>
+      <c r="I5" s="7">
+        <v>1</v>
+      </c>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -889,29 +813,29 @@
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="4">
-        <v>1</v>
-      </c>
-      <c r="D6" s="4">
-        <v>1</v>
-      </c>
-      <c r="E6" s="4">
-        <v>1</v>
-      </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4">
-        <v>1</v>
-      </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="6">
+      <c r="C6" s="3">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -920,31 +844,31 @@
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="4">
-        <v>1</v>
-      </c>
-      <c r="D7" s="4">
-        <v>1</v>
-      </c>
-      <c r="E7" s="4">
-        <v>1</v>
-      </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4">
-        <v>1</v>
-      </c>
-      <c r="H7" s="4">
-        <v>1</v>
-      </c>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="6">
+      <c r="C7" s="3">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3">
+        <v>1</v>
+      </c>
+      <c r="H7" s="3">
+        <v>1</v>
+      </c>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -953,31 +877,31 @@
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="4">
-        <v>1</v>
-      </c>
-      <c r="D8" s="4">
-        <v>1</v>
-      </c>
-      <c r="E8" s="4">
-        <v>1</v>
-      </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4">
-        <v>1</v>
-      </c>
-      <c r="H8" s="4">
-        <v>1</v>
-      </c>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="6">
+      <c r="C8" s="3">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3">
+        <v>1</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1</v>
+      </c>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -986,31 +910,31 @@
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="4">
-        <v>1</v>
-      </c>
-      <c r="D9" s="4">
-        <v>1</v>
-      </c>
-      <c r="E9" s="4">
-        <v>1</v>
-      </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4">
-        <v>1</v>
-      </c>
-      <c r="H9" s="4">
-        <v>1</v>
-      </c>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="6">
+      <c r="C9" s="3">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3">
+        <v>1</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1</v>
+      </c>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -1019,31 +943,31 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="4">
-        <v>1</v>
-      </c>
-      <c r="D10" s="4">
-        <v>1</v>
-      </c>
-      <c r="E10" s="4">
-        <v>1</v>
-      </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4">
-        <v>1</v>
-      </c>
-      <c r="H10" s="8">
-        <v>1</v>
-      </c>
-      <c r="I10" s="5"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="6">
+      <c r="C10" s="3">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3">
+        <v>1</v>
+      </c>
+      <c r="H10" s="6">
+        <v>1</v>
+      </c>
+      <c r="I10" s="4"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -1052,29 +976,29 @@
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="4">
-        <v>1</v>
-      </c>
-      <c r="D11" s="4">
-        <v>1</v>
-      </c>
-      <c r="E11" s="4">
-        <v>1</v>
-      </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4">
-        <v>1</v>
-      </c>
-      <c r="H11" s="4"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="6">
+      <c r="C11" s="3">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3">
+        <v>1</v>
+      </c>
+      <c r="H11" s="3"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1083,29 +1007,29 @@
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="4">
-        <v>1</v>
-      </c>
-      <c r="D12" s="4">
-        <v>1</v>
-      </c>
-      <c r="E12" s="4">
-        <v>1</v>
-      </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4">
-        <v>1</v>
-      </c>
-      <c r="H12" s="4"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="6">
+      <c r="C12" s="3">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3">
+        <v>1</v>
+      </c>
+      <c r="H12" s="3"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1114,29 +1038,29 @@
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="4">
-        <v>1</v>
-      </c>
-      <c r="D13" s="4">
-        <v>1</v>
-      </c>
-      <c r="E13" s="4">
-        <v>1</v>
-      </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4">
-        <v>1</v>
-      </c>
-      <c r="H13" s="4"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="6">
+      <c r="C13" s="3">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3">
+        <v>1</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3">
+        <v>1</v>
+      </c>
+      <c r="H13" s="3"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1145,29 +1069,29 @@
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="4">
-        <v>1</v>
-      </c>
-      <c r="D14" s="4">
-        <v>1</v>
-      </c>
-      <c r="E14" s="4">
-        <v>1</v>
-      </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4">
-        <v>1</v>
-      </c>
-      <c r="H14" s="4"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="6">
+      <c r="C14" s="3">
+        <v>1</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3">
+        <v>1</v>
+      </c>
+      <c r="H14" s="3"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1176,31 +1100,31 @@
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="9">
-        <v>1</v>
-      </c>
-      <c r="D15" s="9">
-        <v>1</v>
-      </c>
-      <c r="E15" s="9">
-        <v>1</v>
-      </c>
-      <c r="F15" s="5"/>
-      <c r="G15" s="9">
-        <v>1</v>
-      </c>
-      <c r="H15" s="9">
-        <v>1</v>
-      </c>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="12"/>
-      <c r="L15" s="12"/>
-      <c r="M15" s="12"/>
-      <c r="N15" s="6">
+      <c r="C15" s="7">
+        <v>1</v>
+      </c>
+      <c r="D15" s="7">
+        <v>1</v>
+      </c>
+      <c r="E15" s="7">
+        <v>1</v>
+      </c>
+      <c r="F15" s="4"/>
+      <c r="G15" s="7">
+        <v>1</v>
+      </c>
+      <c r="H15" s="7">
+        <v>1</v>
+      </c>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -1209,31 +1133,31 @@
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="25" t="s">
+      <c r="B16" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="9">
-        <v>1</v>
-      </c>
-      <c r="D16" s="9">
-        <v>1</v>
-      </c>
-      <c r="E16" s="9">
-        <v>1</v>
-      </c>
-      <c r="F16" s="5"/>
-      <c r="G16" s="9">
-        <v>1</v>
-      </c>
-      <c r="H16" s="5"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="12">
-        <v>1</v>
-      </c>
-      <c r="K16" s="12"/>
-      <c r="L16" s="12"/>
-      <c r="M16" s="12"/>
-      <c r="N16" s="6">
+      <c r="C16" s="7">
+        <v>1</v>
+      </c>
+      <c r="D16" s="7">
+        <v>1</v>
+      </c>
+      <c r="E16" s="7">
+        <v>1</v>
+      </c>
+      <c r="F16" s="4"/>
+      <c r="G16" s="7">
+        <v>1</v>
+      </c>
+      <c r="H16" s="4"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="9">
+        <v>1</v>
+      </c>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -1242,29 +1166,29 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11">
-        <v>1</v>
-      </c>
-      <c r="K17" s="12">
-        <v>1</v>
-      </c>
-      <c r="L17" s="12">
-        <v>1</v>
-      </c>
-      <c r="M17" s="12">
-        <v>1</v>
-      </c>
-      <c r="N17" s="6">
+      <c r="B17" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8">
+        <v>1</v>
+      </c>
+      <c r="K17" s="9">
+        <v>1</v>
+      </c>
+      <c r="L17" s="9">
+        <v>1</v>
+      </c>
+      <c r="M17" s="9">
+        <v>1</v>
+      </c>
+      <c r="N17" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1273,31 +1197,31 @@
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="12">
-        <v>1</v>
-      </c>
-      <c r="I18" s="11">
-        <v>1</v>
-      </c>
-      <c r="J18" s="11">
-        <v>1</v>
-      </c>
-      <c r="K18" s="12">
-        <v>1</v>
-      </c>
-      <c r="L18" s="12">
-        <v>1</v>
-      </c>
-      <c r="M18" s="11"/>
-      <c r="N18" s="6">
+      <c r="B18" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="9">
+        <v>1</v>
+      </c>
+      <c r="I18" s="8">
+        <v>1</v>
+      </c>
+      <c r="J18" s="8">
+        <v>1</v>
+      </c>
+      <c r="K18" s="9">
+        <v>1</v>
+      </c>
+      <c r="L18" s="9">
+        <v>1</v>
+      </c>
+      <c r="M18" s="8"/>
+      <c r="N18" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -1306,25 +1230,25 @@
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="11">
-        <v>1</v>
-      </c>
-      <c r="J19" s="11">
-        <v>1</v>
-      </c>
-      <c r="K19" s="8"/>
-      <c r="L19" s="5"/>
-      <c r="M19" s="5"/>
-      <c r="N19" s="6">
+      <c r="B19" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="8">
+        <v>1</v>
+      </c>
+      <c r="J19" s="8">
+        <v>1</v>
+      </c>
+      <c r="K19" s="6"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -1333,31 +1257,31 @@
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="12">
-        <v>1</v>
-      </c>
-      <c r="I20" s="11">
-        <v>1</v>
-      </c>
-      <c r="J20" s="11">
-        <v>1</v>
-      </c>
-      <c r="K20" s="12">
-        <v>1</v>
-      </c>
-      <c r="L20" s="9">
-        <v>1</v>
-      </c>
-      <c r="M20" s="5"/>
-      <c r="N20" s="6">
+      <c r="B20" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="9">
+        <v>1</v>
+      </c>
+      <c r="I20" s="8">
+        <v>1</v>
+      </c>
+      <c r="J20" s="8">
+        <v>1</v>
+      </c>
+      <c r="K20" s="9">
+        <v>1</v>
+      </c>
+      <c r="L20" s="7">
+        <v>1</v>
+      </c>
+      <c r="M20" s="4"/>
+      <c r="N20" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -1366,29 +1290,29 @@
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="11">
-        <v>1</v>
-      </c>
-      <c r="J21" s="11">
-        <v>1</v>
-      </c>
-      <c r="K21" s="12">
-        <v>1</v>
-      </c>
-      <c r="L21" s="12">
-        <v>1</v>
-      </c>
-      <c r="M21" s="12"/>
-      <c r="N21" s="6">
+      <c r="B21" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="8">
+        <v>1</v>
+      </c>
+      <c r="J21" s="8">
+        <v>1</v>
+      </c>
+      <c r="K21" s="9">
+        <v>1</v>
+      </c>
+      <c r="L21" s="9">
+        <v>1</v>
+      </c>
+      <c r="M21" s="9"/>
+      <c r="N21" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1397,27 +1321,27 @@
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="11">
-        <v>1</v>
-      </c>
-      <c r="J22" s="11">
-        <v>1</v>
-      </c>
-      <c r="K22" s="12">
-        <v>1</v>
-      </c>
-      <c r="L22" s="12"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="6">
+      <c r="B22" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="8">
+        <v>1</v>
+      </c>
+      <c r="J22" s="8">
+        <v>1</v>
+      </c>
+      <c r="K22" s="9">
+        <v>1</v>
+      </c>
+      <c r="L22" s="9"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -1426,29 +1350,29 @@
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="11">
-        <v>1</v>
-      </c>
-      <c r="J23" s="11">
-        <v>1</v>
-      </c>
-      <c r="K23" s="12">
-        <v>1</v>
-      </c>
-      <c r="L23" s="12">
-        <v>1</v>
-      </c>
-      <c r="M23" s="11"/>
-      <c r="N23" s="6">
+      <c r="B23" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="8">
+        <v>1</v>
+      </c>
+      <c r="J23" s="8">
+        <v>1</v>
+      </c>
+      <c r="K23" s="9">
+        <v>1</v>
+      </c>
+      <c r="L23" s="9">
+        <v>1</v>
+      </c>
+      <c r="M23" s="8"/>
+      <c r="N23" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1457,27 +1381,27 @@
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="I24" s="14">
-        <v>1</v>
-      </c>
-      <c r="J24" s="14">
-        <v>1</v>
-      </c>
-      <c r="K24" s="14">
-        <v>1</v>
-      </c>
-      <c r="L24" s="14">
-        <v>1</v>
-      </c>
-      <c r="N24" s="6">
+      <c r="B24" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="I24" s="10">
+        <v>1</v>
+      </c>
+      <c r="J24" s="10">
+        <v>1</v>
+      </c>
+      <c r="K24" s="10">
+        <v>1</v>
+      </c>
+      <c r="L24" s="10">
+        <v>1</v>
+      </c>
+      <c r="N24" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1486,29 +1410,29 @@
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="12">
-        <v>1</v>
-      </c>
-      <c r="I25" s="11">
-        <v>1</v>
-      </c>
-      <c r="J25" s="12">
-        <v>1</v>
-      </c>
-      <c r="K25" s="12">
-        <v>1</v>
-      </c>
-      <c r="L25" s="12"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="6">
+      <c r="B25" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="9">
+        <v>1</v>
+      </c>
+      <c r="I25" s="8">
+        <v>1</v>
+      </c>
+      <c r="J25" s="9">
+        <v>1</v>
+      </c>
+      <c r="K25" s="9">
+        <v>1</v>
+      </c>
+      <c r="L25" s="9"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1517,29 +1441,29 @@
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="12">
-        <v>1</v>
-      </c>
-      <c r="I26" s="11">
-        <v>1</v>
-      </c>
-      <c r="J26" s="12">
-        <v>1</v>
-      </c>
-      <c r="K26" s="12">
-        <v>1</v>
-      </c>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
-      <c r="N26" s="6">
+      <c r="B26" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="9">
+        <v>1</v>
+      </c>
+      <c r="I26" s="8">
+        <v>1</v>
+      </c>
+      <c r="J26" s="9">
+        <v>1</v>
+      </c>
+      <c r="K26" s="9">
+        <v>1</v>
+      </c>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1548,29 +1472,29 @@
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="12">
-        <v>1</v>
-      </c>
-      <c r="I27" s="11">
-        <v>1</v>
-      </c>
-      <c r="J27" s="12">
-        <v>1</v>
-      </c>
-      <c r="K27" s="12">
-        <v>1</v>
-      </c>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="6">
+      <c r="B27" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="9">
+        <v>1</v>
+      </c>
+      <c r="I27" s="8">
+        <v>1</v>
+      </c>
+      <c r="J27" s="9">
+        <v>1</v>
+      </c>
+      <c r="K27" s="9">
+        <v>1</v>
+      </c>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="N27" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1579,27 +1503,27 @@
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9">
-        <v>1</v>
-      </c>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9">
-        <v>1</v>
-      </c>
-      <c r="M28" s="9">
-        <v>1</v>
-      </c>
-      <c r="N28" s="6">
+      <c r="B28" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7">
+        <v>1</v>
+      </c>
+      <c r="K28" s="7"/>
+      <c r="L28" s="7">
+        <v>1</v>
+      </c>
+      <c r="M28" s="7">
+        <v>1</v>
+      </c>
+      <c r="N28" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -1608,29 +1532,29 @@
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="9">
-        <v>1</v>
-      </c>
-      <c r="J29" s="9"/>
-      <c r="K29" s="9">
-        <v>1</v>
-      </c>
-      <c r="L29" s="9">
-        <v>1</v>
-      </c>
-      <c r="M29" s="9">
-        <v>1</v>
-      </c>
-      <c r="N29" s="6">
+      <c r="B29" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="7">
+        <v>1</v>
+      </c>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7">
+        <v>1</v>
+      </c>
+      <c r="L29" s="7">
+        <v>1</v>
+      </c>
+      <c r="M29" s="7">
+        <v>1</v>
+      </c>
+      <c r="N29" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1639,29 +1563,29 @@
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
-      <c r="I30" s="9">
-        <v>1</v>
-      </c>
-      <c r="J30" s="9"/>
-      <c r="K30" s="9">
-        <v>1</v>
-      </c>
-      <c r="L30" s="9">
-        <v>1</v>
-      </c>
-      <c r="M30" s="9">
-        <v>1</v>
-      </c>
-      <c r="N30" s="6">
+      <c r="B30" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="7">
+        <v>1</v>
+      </c>
+      <c r="J30" s="7"/>
+      <c r="K30" s="7">
+        <v>1</v>
+      </c>
+      <c r="L30" s="7">
+        <v>1</v>
+      </c>
+      <c r="M30" s="7">
+        <v>1</v>
+      </c>
+      <c r="N30" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1670,29 +1594,29 @@
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="11"/>
-      <c r="J31" s="12">
-        <v>1</v>
-      </c>
-      <c r="K31" s="12">
-        <v>1</v>
-      </c>
-      <c r="L31" s="12">
-        <v>1</v>
-      </c>
-      <c r="M31" s="12">
-        <v>1</v>
-      </c>
-      <c r="N31" s="6">
+      <c r="B31" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="9">
+        <v>1</v>
+      </c>
+      <c r="K31" s="9">
+        <v>1</v>
+      </c>
+      <c r="L31" s="9">
+        <v>1</v>
+      </c>
+      <c r="M31" s="9">
+        <v>1</v>
+      </c>
+      <c r="N31" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1701,29 +1625,29 @@
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
-      <c r="I32" s="9">
-        <v>1</v>
-      </c>
-      <c r="J32" s="5"/>
-      <c r="K32" s="9">
-        <v>1</v>
-      </c>
-      <c r="L32" s="9">
-        <v>1</v>
-      </c>
-      <c r="M32" s="9">
-        <v>1</v>
-      </c>
-      <c r="N32" s="6">
+      <c r="B32" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="7">
+        <v>1</v>
+      </c>
+      <c r="J32" s="4"/>
+      <c r="K32" s="7">
+        <v>1</v>
+      </c>
+      <c r="L32" s="7">
+        <v>1</v>
+      </c>
+      <c r="M32" s="7">
+        <v>1</v>
+      </c>
+      <c r="N32" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1732,31 +1656,31 @@
       <c r="A33" s="1">
         <v>31</v>
       </c>
-      <c r="B33" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="9">
-        <v>1</v>
-      </c>
-      <c r="I33" s="9">
-        <v>1</v>
-      </c>
-      <c r="J33" s="9">
-        <v>1</v>
-      </c>
-      <c r="K33" s="9">
-        <v>1</v>
-      </c>
-      <c r="L33" s="9">
-        <v>1</v>
-      </c>
-      <c r="M33" s="9"/>
-      <c r="N33" s="6">
+      <c r="B33" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="7">
+        <v>1</v>
+      </c>
+      <c r="I33" s="7">
+        <v>1</v>
+      </c>
+      <c r="J33" s="7">
+        <v>1</v>
+      </c>
+      <c r="K33" s="7">
+        <v>1</v>
+      </c>
+      <c r="L33" s="7">
+        <v>1</v>
+      </c>
+      <c r="M33" s="7"/>
+      <c r="N33" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -1764,49 +1688,49 @@
     <row r="34" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C34" s="6">
+        <v>27</v>
+      </c>
+      <c r="C34" s="5">
         <f t="shared" ref="C34:M34" si="1">SUM(C3:C33)</f>
         <v>11</v>
       </c>
-      <c r="D34" s="6">
+      <c r="D34" s="5">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="E34" s="6">
+      <c r="E34" s="5">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="F34" s="6">
+      <c r="F34" s="5">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G34" s="6">
+      <c r="G34" s="5">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="H34" s="6">
+      <c r="H34" s="5">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="I34" s="6">
+      <c r="I34" s="5">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="J34" s="6">
+      <c r="J34" s="5">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="K34" s="6">
+      <c r="K34" s="5">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="L34" s="6">
+      <c r="L34" s="5">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="M34" s="6">
+      <c r="M34" s="5">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
@@ -5687,7 +5611,7 @@
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.796875" customWidth="1"/>
-    <col min="2" max="2" width="26.09765625" customWidth="1"/>
+    <col min="2" max="2" width="42.296875" customWidth="1"/>
     <col min="3" max="26" width="10.59765625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5745,7 +5669,7 @@
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>1</v>
@@ -5791,454 +5715,454 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
-    <row r="3" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="4">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1</v>
-      </c>
-      <c r="E3" s="4">
-        <v>1</v>
-      </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4">
-        <v>1</v>
-      </c>
-      <c r="H3" s="4">
-        <v>1</v>
-      </c>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="6">
+      <c r="C3" s="3">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3">
+        <v>1</v>
+      </c>
+      <c r="H3" s="3">
+        <v>1</v>
+      </c>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="5">
         <f>SUM(B3:M3)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="8">
-        <v>1</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1</v>
-      </c>
-      <c r="E4" s="4">
-        <v>1</v>
-      </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4">
-        <v>1</v>
-      </c>
-      <c r="H4" s="4">
-        <v>1</v>
-      </c>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="6">
+      <c r="C4" s="6">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3">
+        <v>1</v>
+      </c>
+      <c r="H4" s="3">
+        <v>1</v>
+      </c>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="5">
         <f t="shared" ref="N4:N33" si="0">SUM(C4:M4)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="4">
-        <v>1</v>
-      </c>
-      <c r="E5" s="4">
-        <v>1</v>
-      </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4">
-        <v>1</v>
-      </c>
-      <c r="H5" s="4">
-        <v>1</v>
-      </c>
-      <c r="I5" s="16">
-        <v>1</v>
-      </c>
-      <c r="J5" s="16"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="6">
+      <c r="C5" s="6"/>
+      <c r="D5" s="3">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3">
+        <v>1</v>
+      </c>
+      <c r="H5" s="3">
+        <v>1</v>
+      </c>
+      <c r="I5" s="12">
+        <v>1</v>
+      </c>
+      <c r="J5" s="12"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>6</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="4">
-        <v>1</v>
-      </c>
-      <c r="D6" s="4">
-        <v>1</v>
-      </c>
-      <c r="E6" s="4">
-        <v>1</v>
-      </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4">
-        <v>1</v>
-      </c>
-      <c r="H6" s="4">
-        <v>1</v>
-      </c>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="6">
+      <c r="C6" s="3">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3">
+        <v>1</v>
+      </c>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>7</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="4">
-        <v>1</v>
-      </c>
-      <c r="D7" s="4">
-        <v>1</v>
-      </c>
-      <c r="E7" s="4">
-        <v>1</v>
-      </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4">
-        <v>1</v>
-      </c>
-      <c r="H7" s="4">
-        <v>1</v>
-      </c>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="6">
+      <c r="C7" s="3">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3">
+        <v>1</v>
+      </c>
+      <c r="H7" s="3">
+        <v>1</v>
+      </c>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>8</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="4">
-        <v>1</v>
-      </c>
-      <c r="D8" s="4">
-        <v>1</v>
-      </c>
-      <c r="E8" s="4">
-        <v>1</v>
-      </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4">
-        <v>1</v>
-      </c>
-      <c r="H8" s="4">
-        <v>1</v>
-      </c>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="6">
+      <c r="C8" s="3">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3">
+        <v>1</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1</v>
+      </c>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:26" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>9</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4">
-        <v>1</v>
-      </c>
-      <c r="E9" s="4">
-        <v>1</v>
-      </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4">
-        <v>1</v>
-      </c>
-      <c r="H9" s="4">
-        <v>1</v>
-      </c>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="6">
+      <c r="C9" s="3"/>
+      <c r="D9" s="3">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3">
+        <v>1</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1</v>
+      </c>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>10</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4">
-        <v>1</v>
-      </c>
-      <c r="E10" s="4">
-        <v>1</v>
-      </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4">
-        <v>1</v>
-      </c>
-      <c r="H10" s="4">
-        <v>1</v>
-      </c>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="6">
+      <c r="C10" s="3"/>
+      <c r="D10" s="3">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3">
+        <v>1</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1</v>
+      </c>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:26" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>11</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4">
-        <v>1</v>
-      </c>
-      <c r="E11" s="4">
-        <v>1</v>
-      </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4">
-        <v>1</v>
-      </c>
-      <c r="H11" s="4">
-        <v>1</v>
-      </c>
-      <c r="I11" s="16">
-        <v>1</v>
-      </c>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="6">
+      <c r="C11" s="3"/>
+      <c r="D11" s="3">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3">
+        <v>1</v>
+      </c>
+      <c r="H11" s="3">
+        <v>1</v>
+      </c>
+      <c r="I11" s="12">
+        <v>1</v>
+      </c>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>12</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="4">
-        <v>1</v>
-      </c>
-      <c r="D12" s="4">
-        <v>1</v>
-      </c>
-      <c r="E12" s="4">
-        <v>1</v>
-      </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4">
-        <v>1</v>
-      </c>
-      <c r="H12" s="4">
-        <v>1</v>
-      </c>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="6">
+      <c r="C12" s="3">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3">
+        <v>1</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1</v>
+      </c>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>13</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="4">
-        <v>1</v>
-      </c>
-      <c r="D13" s="4">
-        <v>1</v>
-      </c>
-      <c r="E13" s="4">
-        <v>1</v>
-      </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4">
-        <v>1</v>
-      </c>
-      <c r="H13" s="4">
-        <v>1</v>
-      </c>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="6">
+      <c r="C13" s="3">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3">
+        <v>1</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3">
+        <v>1</v>
+      </c>
+      <c r="H13" s="3">
+        <v>1</v>
+      </c>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:26" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>14</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4">
-        <v>1</v>
-      </c>
-      <c r="E14" s="4">
-        <v>1</v>
-      </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4">
-        <v>1</v>
-      </c>
-      <c r="H14" s="4">
-        <v>1</v>
-      </c>
-      <c r="I14" s="16">
-        <v>1</v>
-      </c>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="6">
+      <c r="C14" s="3"/>
+      <c r="D14" s="3">
+        <v>1</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3">
+        <v>1</v>
+      </c>
+      <c r="H14" s="3">
+        <v>1</v>
+      </c>
+      <c r="I14" s="12">
+        <v>1</v>
+      </c>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1"/>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16">
-        <v>1</v>
-      </c>
-      <c r="E15" s="16">
-        <v>1</v>
-      </c>
-      <c r="F15" s="15"/>
-      <c r="G15" s="16">
-        <v>1</v>
-      </c>
-      <c r="H15" s="16">
-        <v>1</v>
-      </c>
-      <c r="I15" s="15"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="6">
+      <c r="C15" s="12"/>
+      <c r="D15" s="12">
+        <v>1</v>
+      </c>
+      <c r="E15" s="12">
+        <v>1</v>
+      </c>
+      <c r="F15" s="11"/>
+      <c r="G15" s="12">
+        <v>1</v>
+      </c>
+      <c r="H15" s="12">
+        <v>1</v>
+      </c>
+      <c r="I15" s="11"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="16">
-        <v>1</v>
-      </c>
-      <c r="D16" s="16">
-        <v>1</v>
-      </c>
-      <c r="E16" s="16">
-        <v>1</v>
-      </c>
-      <c r="F16" s="15"/>
-      <c r="G16" s="16">
-        <v>1</v>
-      </c>
-      <c r="H16" s="16">
-        <v>1</v>
-      </c>
-      <c r="I16" s="15"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="6">
+      <c r="C16" s="12">
+        <v>1</v>
+      </c>
+      <c r="D16" s="12">
+        <v>1</v>
+      </c>
+      <c r="E16" s="12">
+        <v>1</v>
+      </c>
+      <c r="F16" s="11"/>
+      <c r="G16" s="12">
+        <v>1</v>
+      </c>
+      <c r="H16" s="12">
+        <v>1</v>
+      </c>
+      <c r="I16" s="11"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -6247,27 +6171,27 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="16">
-        <v>1</v>
-      </c>
-      <c r="K17" s="16">
-        <v>1</v>
-      </c>
-      <c r="L17" s="16">
-        <v>1</v>
-      </c>
-      <c r="M17" s="16"/>
-      <c r="N17" s="6">
+      <c r="B17" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="12"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="12">
+        <v>1</v>
+      </c>
+      <c r="K17" s="12">
+        <v>1</v>
+      </c>
+      <c r="L17" s="12">
+        <v>1</v>
+      </c>
+      <c r="M17" s="12"/>
+      <c r="N17" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -6276,27 +6200,27 @@
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="16">
-        <v>1</v>
-      </c>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="16">
-        <v>1</v>
-      </c>
-      <c r="L18" s="16">
-        <v>1</v>
-      </c>
-      <c r="M18" s="15"/>
-      <c r="N18" s="6">
+      <c r="B18" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="12">
+        <v>1</v>
+      </c>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="12">
+        <v>1</v>
+      </c>
+      <c r="L18" s="12">
+        <v>1</v>
+      </c>
+      <c r="M18" s="11"/>
+      <c r="N18" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -6305,29 +6229,29 @@
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" s="16">
-        <v>1</v>
-      </c>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="16">
-        <v>1</v>
-      </c>
-      <c r="K19" s="16">
-        <v>1</v>
-      </c>
-      <c r="L19" s="16">
-        <v>1</v>
-      </c>
-      <c r="M19" s="15"/>
-      <c r="N19" s="6">
+      <c r="B19" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="12">
+        <v>1</v>
+      </c>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="12">
+        <v>1</v>
+      </c>
+      <c r="K19" s="12">
+        <v>1</v>
+      </c>
+      <c r="L19" s="12">
+        <v>1</v>
+      </c>
+      <c r="M19" s="11"/>
+      <c r="N19" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -6336,27 +6260,27 @@
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="16">
-        <v>1</v>
-      </c>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="16">
-        <v>1</v>
-      </c>
-      <c r="L20" s="16">
-        <v>1</v>
-      </c>
-      <c r="M20" s="15"/>
-      <c r="N20" s="6">
+      <c r="B20" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="12">
+        <v>1</v>
+      </c>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="12">
+        <v>1</v>
+      </c>
+      <c r="L20" s="12">
+        <v>1</v>
+      </c>
+      <c r="M20" s="11"/>
+      <c r="N20" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -6365,29 +6289,29 @@
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" s="16">
-        <v>1</v>
-      </c>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="16">
-        <v>1</v>
-      </c>
-      <c r="K21" s="16">
-        <v>1</v>
-      </c>
-      <c r="L21" s="16">
-        <v>1</v>
-      </c>
-      <c r="M21" s="16"/>
-      <c r="N21" s="6">
+      <c r="B21" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="12">
+        <v>1</v>
+      </c>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="12">
+        <v>1</v>
+      </c>
+      <c r="K21" s="12">
+        <v>1</v>
+      </c>
+      <c r="L21" s="12">
+        <v>1</v>
+      </c>
+      <c r="M21" s="12"/>
+      <c r="N21" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -6396,27 +6320,27 @@
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
-      <c r="J22" s="15"/>
-      <c r="K22" s="16">
-        <v>1</v>
-      </c>
-      <c r="L22" s="16">
-        <v>1</v>
-      </c>
-      <c r="M22" s="16">
-        <v>1</v>
-      </c>
-      <c r="N22" s="6">
+      <c r="B22" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="12">
+        <v>1</v>
+      </c>
+      <c r="L22" s="12">
+        <v>1</v>
+      </c>
+      <c r="M22" s="12">
+        <v>1</v>
+      </c>
+      <c r="N22" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -6425,25 +6349,25 @@
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="16">
-        <v>1</v>
-      </c>
-      <c r="K23" s="16">
-        <v>1</v>
-      </c>
-      <c r="L23" s="16"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="6">
+      <c r="B23" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="12">
+        <v>1</v>
+      </c>
+      <c r="K23" s="12">
+        <v>1</v>
+      </c>
+      <c r="L23" s="12"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -6452,27 +6376,27 @@
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="18">
-        <v>1</v>
-      </c>
-      <c r="K24" s="18">
-        <v>1</v>
-      </c>
-      <c r="L24" s="18">
-        <v>1</v>
-      </c>
-      <c r="M24" s="17"/>
-      <c r="N24" s="6">
+      <c r="B24" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="14">
+        <v>1</v>
+      </c>
+      <c r="K24" s="14">
+        <v>1</v>
+      </c>
+      <c r="L24" s="14">
+        <v>1</v>
+      </c>
+      <c r="M24" s="13"/>
+      <c r="N24" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -6481,29 +6405,29 @@
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16">
-        <v>1</v>
-      </c>
-      <c r="J25" s="16">
-        <v>1</v>
-      </c>
-      <c r="K25" s="16">
-        <v>1</v>
-      </c>
-      <c r="L25" s="16">
-        <v>1</v>
-      </c>
-      <c r="M25" s="15"/>
-      <c r="N25" s="6">
+      <c r="B25" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12">
+        <v>1</v>
+      </c>
+      <c r="J25" s="12">
+        <v>1</v>
+      </c>
+      <c r="K25" s="12">
+        <v>1</v>
+      </c>
+      <c r="L25" s="12">
+        <v>1</v>
+      </c>
+      <c r="M25" s="11"/>
+      <c r="N25" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -6512,29 +6436,29 @@
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16">
-        <v>1</v>
-      </c>
-      <c r="J26" s="16">
-        <v>1</v>
-      </c>
-      <c r="K26" s="16">
-        <v>1</v>
-      </c>
-      <c r="L26" s="16">
-        <v>1</v>
-      </c>
-      <c r="M26" s="15"/>
-      <c r="N26" s="6">
+      <c r="B26" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12">
+        <v>1</v>
+      </c>
+      <c r="J26" s="12">
+        <v>1</v>
+      </c>
+      <c r="K26" s="12">
+        <v>1</v>
+      </c>
+      <c r="L26" s="12">
+        <v>1</v>
+      </c>
+      <c r="M26" s="11"/>
+      <c r="N26" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -6543,29 +6467,29 @@
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="16">
-        <v>1</v>
-      </c>
-      <c r="J27" s="16">
-        <v>1</v>
-      </c>
-      <c r="K27" s="16">
-        <v>1</v>
-      </c>
-      <c r="L27" s="16">
-        <v>1</v>
-      </c>
-      <c r="M27" s="15"/>
-      <c r="N27" s="6">
+      <c r="B27" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12">
+        <v>1</v>
+      </c>
+      <c r="J27" s="12">
+        <v>1</v>
+      </c>
+      <c r="K27" s="12">
+        <v>1</v>
+      </c>
+      <c r="L27" s="12">
+        <v>1</v>
+      </c>
+      <c r="M27" s="11"/>
+      <c r="N27" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -6574,29 +6498,29 @@
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C28" s="16"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="16">
-        <v>1</v>
-      </c>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
-      <c r="J28" s="15"/>
-      <c r="K28" s="16">
-        <v>1</v>
-      </c>
-      <c r="L28" s="16">
-        <v>1</v>
-      </c>
-      <c r="M28" s="16">
-        <v>1</v>
-      </c>
-      <c r="N28" s="6">
+      <c r="B28" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" s="12"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="12">
+        <v>1</v>
+      </c>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="12">
+        <v>1</v>
+      </c>
+      <c r="L28" s="12">
+        <v>1</v>
+      </c>
+      <c r="M28" s="12">
+        <v>1</v>
+      </c>
+      <c r="N28" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -6605,27 +6529,27 @@
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C29" s="16"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
-      <c r="J29" s="15"/>
-      <c r="K29" s="16">
-        <v>1</v>
-      </c>
-      <c r="L29" s="16">
-        <v>1</v>
-      </c>
-      <c r="M29" s="16">
-        <v>1</v>
-      </c>
-      <c r="N29" s="6">
+      <c r="B29" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" s="12"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="12">
+        <v>1</v>
+      </c>
+      <c r="L29" s="12">
+        <v>1</v>
+      </c>
+      <c r="M29" s="12">
+        <v>1</v>
+      </c>
+      <c r="N29" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -6634,27 +6558,27 @@
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="16">
-        <v>1</v>
-      </c>
-      <c r="L30" s="16">
-        <v>1</v>
-      </c>
-      <c r="M30" s="16">
-        <v>1</v>
-      </c>
-      <c r="N30" s="6">
+      <c r="B30" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="12"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="12">
+        <v>1</v>
+      </c>
+      <c r="L30" s="12">
+        <v>1</v>
+      </c>
+      <c r="M30" s="12">
+        <v>1</v>
+      </c>
+      <c r="N30" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -6663,23 +6587,23 @@
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="16">
-        <v>1</v>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="15"/>
-      <c r="N31" s="6">
+      <c r="B31" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" s="12"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="12">
+        <v>1</v>
+      </c>
+      <c r="K31" s="12"/>
+      <c r="L31" s="12"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="5">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -6688,25 +6612,25 @@
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C32" s="16"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="16">
-        <v>1</v>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16">
-        <v>1</v>
-      </c>
-      <c r="M32" s="16"/>
-      <c r="N32" s="6">
+      <c r="B32" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" s="12"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="12">
+        <v>1</v>
+      </c>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12">
+        <v>1</v>
+      </c>
+      <c r="M32" s="12"/>
+      <c r="N32" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -6715,25 +6639,25 @@
       <c r="A33" s="1">
         <v>31</v>
       </c>
-      <c r="B33" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C33" s="16"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="15"/>
-      <c r="J33" s="15"/>
-      <c r="K33" s="16">
-        <v>1</v>
-      </c>
-      <c r="L33" s="16">
-        <v>1</v>
-      </c>
-      <c r="M33" s="16"/>
-      <c r="N33" s="6">
+      <c r="B33" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" s="12"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="12">
+        <v>1</v>
+      </c>
+      <c r="L33" s="12">
+        <v>1</v>
+      </c>
+      <c r="M33" s="12"/>
+      <c r="N33" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -6741,49 +6665,49 @@
     <row r="34" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C34" s="6">
+        <v>27</v>
+      </c>
+      <c r="C34" s="5">
         <f t="shared" ref="C34:M34" si="1">SUM(C3:C33)</f>
         <v>12</v>
       </c>
-      <c r="D34" s="6">
+      <c r="D34" s="5">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="E34" s="6">
+      <c r="E34" s="5">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="F34" s="6">
+      <c r="F34" s="5">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="G34" s="6">
+      <c r="G34" s="5">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="H34" s="6">
+      <c r="H34" s="5">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="I34" s="6">
+      <c r="I34" s="5">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="J34" s="6">
+      <c r="J34" s="5">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="K34" s="6">
+      <c r="K34" s="5">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="L34" s="6">
+      <c r="L34" s="5">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="M34" s="6">
+      <c r="M34" s="5">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -10664,7 +10588,7 @@
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.09765625" customWidth="1"/>
-    <col min="2" max="2" width="26.09765625" customWidth="1"/>
+    <col min="2" max="2" width="42.296875" customWidth="1"/>
     <col min="3" max="12" width="10.59765625" customWidth="1"/>
     <col min="13" max="13" width="6.296875" customWidth="1"/>
     <col min="14" max="26" width="10.59765625" customWidth="1"/>
@@ -10724,7 +10648,7 @@
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>1</v>
@@ -10770,456 +10694,456 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
-    <row r="3" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="4">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1</v>
-      </c>
-      <c r="E3" s="4">
-        <v>1</v>
-      </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4">
-        <v>1</v>
-      </c>
-      <c r="H3" s="4">
-        <v>1</v>
-      </c>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="6">
+      <c r="C3" s="3">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3">
+        <v>1</v>
+      </c>
+      <c r="H3" s="3">
+        <v>1</v>
+      </c>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="5">
         <f t="shared" ref="N3:N33" si="0">SUM(C3:M3)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4">
-        <v>1</v>
-      </c>
-      <c r="E4" s="4">
-        <v>1</v>
-      </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4">
-        <v>1</v>
-      </c>
-      <c r="H4" s="4">
-        <v>1</v>
-      </c>
-      <c r="I4" s="16">
-        <v>1</v>
-      </c>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="6">
+      <c r="C4" s="3"/>
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3">
+        <v>1</v>
+      </c>
+      <c r="H4" s="3">
+        <v>1</v>
+      </c>
+      <c r="I4" s="12">
+        <v>1</v>
+      </c>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4">
-        <v>1</v>
-      </c>
-      <c r="E5" s="4">
-        <v>1</v>
-      </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4">
-        <v>1</v>
-      </c>
-      <c r="H5" s="4">
-        <v>1</v>
-      </c>
-      <c r="I5" s="16">
-        <v>1</v>
-      </c>
-      <c r="J5" s="16"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="6">
+      <c r="C5" s="3"/>
+      <c r="D5" s="3">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3">
+        <v>1</v>
+      </c>
+      <c r="H5" s="3">
+        <v>1</v>
+      </c>
+      <c r="I5" s="12">
+        <v>1</v>
+      </c>
+      <c r="J5" s="12"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>6</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="4">
-        <v>1</v>
-      </c>
-      <c r="D6" s="4">
-        <v>1</v>
-      </c>
-      <c r="E6" s="4">
-        <v>1</v>
-      </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4">
-        <v>1</v>
-      </c>
-      <c r="H6" s="4">
-        <v>1</v>
-      </c>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="6">
+      <c r="C6" s="3">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3">
+        <v>1</v>
+      </c>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>7</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="4">
-        <v>1</v>
-      </c>
-      <c r="D7" s="4">
-        <v>1</v>
-      </c>
-      <c r="E7" s="4">
-        <v>1</v>
-      </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4">
-        <v>1</v>
-      </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="6">
+      <c r="C7" s="3">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3">
+        <v>1</v>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>8</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4">
-        <v>1</v>
-      </c>
-      <c r="E8" s="4">
-        <v>1</v>
-      </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4">
-        <v>1</v>
-      </c>
-      <c r="H8" s="4">
-        <v>1</v>
-      </c>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="6">
+      <c r="C8" s="3"/>
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3">
+        <v>1</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1</v>
+      </c>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:26" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>9</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="4">
-        <v>1</v>
-      </c>
-      <c r="D9" s="4">
-        <v>1</v>
-      </c>
-      <c r="E9" s="4">
-        <v>1</v>
-      </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4">
-        <v>1</v>
-      </c>
-      <c r="H9" s="4">
-        <v>1</v>
-      </c>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="6">
+      <c r="C9" s="3">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3">
+        <v>1</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1</v>
+      </c>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>10</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="4">
-        <v>1</v>
-      </c>
-      <c r="D10" s="4">
-        <v>1</v>
-      </c>
-      <c r="E10" s="4">
-        <v>1</v>
-      </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4">
-        <v>1</v>
-      </c>
-      <c r="H10" s="4">
-        <v>1</v>
-      </c>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="6">
+      <c r="C10" s="3">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3">
+        <v>1</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1</v>
+      </c>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:26" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>11</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="4">
-        <v>1</v>
-      </c>
-      <c r="D11" s="4">
-        <v>1</v>
-      </c>
-      <c r="E11" s="4">
-        <v>1</v>
-      </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4">
-        <v>1</v>
-      </c>
-      <c r="H11" s="4">
-        <v>1</v>
-      </c>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="6">
+      <c r="C11" s="3">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3">
+        <v>1</v>
+      </c>
+      <c r="H11" s="3">
+        <v>1</v>
+      </c>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>12</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="4">
-        <v>1</v>
-      </c>
-      <c r="D12" s="4">
-        <v>1</v>
-      </c>
-      <c r="E12" s="4">
-        <v>1</v>
-      </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4">
-        <v>1</v>
-      </c>
-      <c r="H12" s="4">
-        <v>1</v>
-      </c>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="6">
+      <c r="C12" s="3">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3">
+        <v>1</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1</v>
+      </c>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>13</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="4">
-        <v>1</v>
-      </c>
-      <c r="D13" s="4">
-        <v>1</v>
-      </c>
-      <c r="E13" s="4">
-        <v>1</v>
-      </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4">
-        <v>1</v>
-      </c>
-      <c r="H13" s="4">
-        <v>1</v>
-      </c>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="6">
+      <c r="C13" s="3">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3">
+        <v>1</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3">
+        <v>1</v>
+      </c>
+      <c r="H13" s="3">
+        <v>1</v>
+      </c>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:26" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>14</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="4">
-        <v>1</v>
-      </c>
-      <c r="D14" s="4">
-        <v>1</v>
-      </c>
-      <c r="E14" s="4">
-        <v>1</v>
-      </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4">
-        <v>1</v>
-      </c>
-      <c r="H14" s="4">
-        <v>1</v>
-      </c>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="6">
+      <c r="C14" s="3">
+        <v>1</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3">
+        <v>1</v>
+      </c>
+      <c r="H14" s="3">
+        <v>1</v>
+      </c>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1"/>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="16">
-        <v>1</v>
-      </c>
-      <c r="D15" s="16">
-        <v>1</v>
-      </c>
-      <c r="E15" s="16">
-        <v>1</v>
-      </c>
-      <c r="F15" s="15"/>
-      <c r="G15" s="16">
-        <v>1</v>
-      </c>
-      <c r="H15" s="16">
-        <v>1</v>
-      </c>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="6">
+      <c r="C15" s="12">
+        <v>1</v>
+      </c>
+      <c r="D15" s="12">
+        <v>1</v>
+      </c>
+      <c r="E15" s="12">
+        <v>1</v>
+      </c>
+      <c r="F15" s="11"/>
+      <c r="G15" s="12">
+        <v>1</v>
+      </c>
+      <c r="H15" s="12">
+        <v>1</v>
+      </c>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="16">
-        <v>1</v>
-      </c>
-      <c r="D16" s="16">
-        <v>1</v>
-      </c>
-      <c r="E16" s="16">
-        <v>1</v>
-      </c>
-      <c r="F16" s="15"/>
-      <c r="G16" s="16">
-        <v>1</v>
-      </c>
-      <c r="H16" s="16">
-        <v>1</v>
-      </c>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="6">
+      <c r="C16" s="12">
+        <v>1</v>
+      </c>
+      <c r="D16" s="12">
+        <v>1</v>
+      </c>
+      <c r="E16" s="12">
+        <v>1</v>
+      </c>
+      <c r="F16" s="11"/>
+      <c r="G16" s="12">
+        <v>1</v>
+      </c>
+      <c r="H16" s="12">
+        <v>1</v>
+      </c>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -11228,25 +11152,25 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16">
-        <v>1</v>
-      </c>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16">
-        <v>1</v>
-      </c>
-      <c r="N17" s="6">
+      <c r="B17" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="12"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12">
+        <v>1</v>
+      </c>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12">
+        <v>1</v>
+      </c>
+      <c r="N17" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -11255,29 +11179,29 @@
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16">
-        <v>1</v>
-      </c>
-      <c r="J18" s="16">
-        <v>1</v>
-      </c>
-      <c r="K18" s="16">
-        <v>1</v>
-      </c>
-      <c r="L18" s="16">
-        <v>1</v>
-      </c>
-      <c r="M18" s="15"/>
-      <c r="N18" s="6">
+      <c r="B18" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12">
+        <v>1</v>
+      </c>
+      <c r="J18" s="12">
+        <v>1</v>
+      </c>
+      <c r="K18" s="12">
+        <v>1</v>
+      </c>
+      <c r="L18" s="12">
+        <v>1</v>
+      </c>
+      <c r="M18" s="11"/>
+      <c r="N18" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -11286,27 +11210,27 @@
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" s="16">
-        <v>1</v>
-      </c>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="16">
-        <v>1</v>
-      </c>
-      <c r="L19" s="16">
-        <v>1</v>
-      </c>
-      <c r="M19" s="15"/>
-      <c r="N19" s="6">
+      <c r="B19" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="12">
+        <v>1</v>
+      </c>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="12">
+        <v>1</v>
+      </c>
+      <c r="L19" s="12">
+        <v>1</v>
+      </c>
+      <c r="M19" s="11"/>
+      <c r="N19" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -11315,29 +11239,29 @@
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16">
-        <v>1</v>
-      </c>
-      <c r="J20" s="16">
-        <v>1</v>
-      </c>
-      <c r="K20" s="16">
-        <v>1</v>
-      </c>
-      <c r="L20" s="16">
-        <v>1</v>
-      </c>
-      <c r="M20" s="15"/>
-      <c r="N20" s="6">
+      <c r="B20" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12">
+        <v>1</v>
+      </c>
+      <c r="J20" s="12">
+        <v>1</v>
+      </c>
+      <c r="K20" s="12">
+        <v>1</v>
+      </c>
+      <c r="L20" s="12">
+        <v>1</v>
+      </c>
+      <c r="M20" s="11"/>
+      <c r="N20" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -11346,25 +11270,25 @@
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" s="16">
-        <v>1</v>
-      </c>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="16">
-        <v>1</v>
-      </c>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="6">
+      <c r="B21" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="12">
+        <v>1</v>
+      </c>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="12">
+        <v>1</v>
+      </c>
+      <c r="L21" s="12"/>
+      <c r="M21" s="12"/>
+      <c r="N21" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -11373,27 +11297,27 @@
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
-      <c r="J22" s="16">
-        <v>1</v>
-      </c>
-      <c r="K22" s="16">
-        <v>1</v>
-      </c>
-      <c r="L22" s="16">
-        <v>1</v>
-      </c>
-      <c r="M22" s="15"/>
-      <c r="N22" s="6">
+      <c r="B22" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="12">
+        <v>1</v>
+      </c>
+      <c r="K22" s="12">
+        <v>1</v>
+      </c>
+      <c r="L22" s="12">
+        <v>1</v>
+      </c>
+      <c r="M22" s="11"/>
+      <c r="N22" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -11402,27 +11326,27 @@
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="16">
-        <v>1</v>
-      </c>
-      <c r="K23" s="16">
-        <v>1</v>
-      </c>
-      <c r="L23" s="16">
-        <v>1</v>
-      </c>
-      <c r="M23" s="15"/>
-      <c r="N23" s="6">
+      <c r="B23" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="12">
+        <v>1</v>
+      </c>
+      <c r="K23" s="12">
+        <v>1</v>
+      </c>
+      <c r="L23" s="12">
+        <v>1</v>
+      </c>
+      <c r="M23" s="11"/>
+      <c r="N23" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -11431,25 +11355,25 @@
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="18">
-        <v>1</v>
-      </c>
-      <c r="K24" s="18"/>
-      <c r="L24" s="18">
-        <v>1</v>
-      </c>
-      <c r="M24" s="17"/>
-      <c r="N24" s="6">
+      <c r="B24" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="14">
+        <v>1</v>
+      </c>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14">
+        <v>1</v>
+      </c>
+      <c r="M24" s="13"/>
+      <c r="N24" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -11458,25 +11382,25 @@
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="16">
-        <v>1</v>
-      </c>
-      <c r="L25" s="16">
-        <v>1</v>
-      </c>
-      <c r="M25" s="15"/>
-      <c r="N25" s="6">
+      <c r="B25" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="12">
+        <v>1</v>
+      </c>
+      <c r="L25" s="12">
+        <v>1</v>
+      </c>
+      <c r="M25" s="11"/>
+      <c r="N25" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -11485,25 +11409,25 @@
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="16"/>
-      <c r="K26" s="16">
-        <v>1</v>
-      </c>
-      <c r="L26" s="16">
-        <v>1</v>
-      </c>
-      <c r="M26" s="15"/>
-      <c r="N26" s="6">
+      <c r="B26" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12">
+        <v>1</v>
+      </c>
+      <c r="L26" s="12">
+        <v>1</v>
+      </c>
+      <c r="M26" s="11"/>
+      <c r="N26" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -11512,25 +11436,25 @@
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="16"/>
-      <c r="K27" s="16">
-        <v>1</v>
-      </c>
-      <c r="L27" s="16">
-        <v>1</v>
-      </c>
-      <c r="M27" s="15"/>
-      <c r="N27" s="6">
+      <c r="B27" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12">
+        <v>1</v>
+      </c>
+      <c r="L27" s="12">
+        <v>1</v>
+      </c>
+      <c r="M27" s="11"/>
+      <c r="N27" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -11539,27 +11463,27 @@
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
-      <c r="J28" s="15"/>
-      <c r="K28" s="16">
-        <v>1</v>
-      </c>
-      <c r="L28" s="16">
-        <v>1</v>
-      </c>
-      <c r="M28" s="16">
-        <v>1</v>
-      </c>
-      <c r="N28" s="6">
+      <c r="B28" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="12">
+        <v>1</v>
+      </c>
+      <c r="L28" s="12">
+        <v>1</v>
+      </c>
+      <c r="M28" s="12">
+        <v>1</v>
+      </c>
+      <c r="N28" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -11568,31 +11492,31 @@
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="16">
-        <v>1</v>
-      </c>
-      <c r="J29" s="16">
-        <v>1</v>
-      </c>
-      <c r="K29" s="16">
-        <v>1</v>
-      </c>
-      <c r="L29" s="16">
-        <v>1</v>
-      </c>
-      <c r="M29" s="16">
-        <v>1</v>
-      </c>
-      <c r="N29" s="6">
+      <c r="B29" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="12">
+        <v>1</v>
+      </c>
+      <c r="J29" s="12">
+        <v>1</v>
+      </c>
+      <c r="K29" s="12">
+        <v>1</v>
+      </c>
+      <c r="L29" s="12">
+        <v>1</v>
+      </c>
+      <c r="M29" s="12">
+        <v>1</v>
+      </c>
+      <c r="N29" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -11601,31 +11525,31 @@
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="16">
-        <v>1</v>
-      </c>
-      <c r="J30" s="16">
-        <v>1</v>
-      </c>
-      <c r="K30" s="16">
-        <v>1</v>
-      </c>
-      <c r="L30" s="16">
-        <v>1</v>
-      </c>
-      <c r="M30" s="16">
-        <v>1</v>
-      </c>
-      <c r="N30" s="6">
+      <c r="B30" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="12">
+        <v>1</v>
+      </c>
+      <c r="J30" s="12">
+        <v>1</v>
+      </c>
+      <c r="K30" s="12">
+        <v>1</v>
+      </c>
+      <c r="L30" s="12">
+        <v>1</v>
+      </c>
+      <c r="M30" s="12">
+        <v>1</v>
+      </c>
+      <c r="N30" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -11634,27 +11558,27 @@
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="16"/>
-      <c r="K31" s="16">
-        <v>1</v>
-      </c>
-      <c r="L31" s="16">
-        <v>1</v>
-      </c>
-      <c r="M31" s="16">
-        <v>1</v>
-      </c>
-      <c r="N31" s="6">
+      <c r="B31" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" s="12"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="12">
+        <v>1</v>
+      </c>
+      <c r="L31" s="12">
+        <v>1</v>
+      </c>
+      <c r="M31" s="12">
+        <v>1</v>
+      </c>
+      <c r="N31" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -11663,25 +11587,25 @@
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C32" s="16"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="16">
-        <v>1</v>
-      </c>
-      <c r="K32" s="15"/>
-      <c r="L32" s="16">
-        <v>1</v>
-      </c>
-      <c r="M32" s="16"/>
-      <c r="N32" s="6">
+      <c r="B32" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" s="12"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="12">
+        <v>1</v>
+      </c>
+      <c r="K32" s="11"/>
+      <c r="L32" s="12">
+        <v>1</v>
+      </c>
+      <c r="M32" s="12"/>
+      <c r="N32" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -11690,29 +11614,29 @@
       <c r="A33" s="1">
         <v>31</v>
       </c>
-      <c r="B33" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="16">
-        <v>1</v>
-      </c>
-      <c r="J33" s="16">
-        <v>1</v>
-      </c>
-      <c r="K33" s="16">
-        <v>1</v>
-      </c>
-      <c r="L33" s="16">
-        <v>1</v>
-      </c>
-      <c r="M33" s="15"/>
-      <c r="N33" s="6">
+      <c r="B33" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="12">
+        <v>1</v>
+      </c>
+      <c r="J33" s="12">
+        <v>1</v>
+      </c>
+      <c r="K33" s="12">
+        <v>1</v>
+      </c>
+      <c r="L33" s="12">
+        <v>1</v>
+      </c>
+      <c r="M33" s="11"/>
+      <c r="N33" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -11720,49 +11644,49 @@
     <row r="34" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C34" s="6">
+        <v>27</v>
+      </c>
+      <c r="C34" s="5">
         <f t="shared" ref="C34:M34" si="1">SUM(C3:C33)</f>
         <v>13</v>
       </c>
-      <c r="D34" s="6">
+      <c r="D34" s="5">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="E34" s="6">
+      <c r="E34" s="5">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="F34" s="6">
+      <c r="F34" s="5">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G34" s="6">
+      <c r="G34" s="5">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="H34" s="6">
+      <c r="H34" s="5">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="I34" s="6">
+      <c r="I34" s="5">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="J34" s="6">
+      <c r="J34" s="5">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="K34" s="6">
+      <c r="K34" s="5">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="L34" s="6">
+      <c r="L34" s="5">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="M34" s="6">
+      <c r="M34" s="5">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
@@ -15643,7 +15567,7 @@
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.09765625" customWidth="1"/>
-    <col min="2" max="2" width="26.09765625" customWidth="1"/>
+    <col min="2" max="2" width="42.296875" customWidth="1"/>
     <col min="3" max="8" width="10.59765625" customWidth="1"/>
     <col min="9" max="9" width="8.69921875" customWidth="1"/>
     <col min="10" max="12" width="10.59765625" customWidth="1"/>
@@ -15705,7 +15629,7 @@
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>1</v>
@@ -15751,430 +15675,430 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
-    <row r="3" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4">
-        <v>1</v>
-      </c>
-      <c r="F3" s="8">
-        <v>1</v>
-      </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4">
-        <v>1</v>
-      </c>
-      <c r="I3" s="16">
-        <v>1</v>
-      </c>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="6">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="6">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3">
+        <v>1</v>
+      </c>
+      <c r="I3" s="12">
+        <v>1</v>
+      </c>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="5">
         <f t="shared" ref="N3:N33" si="0">SUM(C3:M3)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4">
-        <v>1</v>
-      </c>
-      <c r="F4" s="8">
-        <v>1</v>
-      </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4">
-        <v>1</v>
-      </c>
-      <c r="I4" s="16">
-        <v>1</v>
-      </c>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="6">
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3">
+        <v>1</v>
+      </c>
+      <c r="F4" s="6">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3">
+        <v>1</v>
+      </c>
+      <c r="I4" s="12">
+        <v>1</v>
+      </c>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4">
-        <v>1</v>
-      </c>
-      <c r="F5" s="8">
-        <v>1</v>
-      </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4">
-        <v>1</v>
-      </c>
-      <c r="I5" s="16">
-        <v>1</v>
-      </c>
-      <c r="J5" s="16"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="6">
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3">
+        <v>1</v>
+      </c>
+      <c r="F5" s="6">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3">
+        <v>1</v>
+      </c>
+      <c r="I5" s="12">
+        <v>1</v>
+      </c>
+      <c r="J5" s="12"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4">
-        <v>1</v>
-      </c>
-      <c r="F6" s="8">
-        <v>1</v>
-      </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4">
-        <v>1</v>
-      </c>
-      <c r="I6" s="16">
-        <v>1</v>
-      </c>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="6">
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3">
+        <v>1</v>
+      </c>
+      <c r="F6" s="6">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3">
+        <v>1</v>
+      </c>
+      <c r="I6" s="12">
+        <v>1</v>
+      </c>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4">
-        <v>1</v>
-      </c>
-      <c r="F7" s="8">
-        <v>1</v>
-      </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4">
-        <v>1</v>
-      </c>
-      <c r="I7" s="16">
-        <v>1</v>
-      </c>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="6">
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3">
+        <v>1</v>
+      </c>
+      <c r="F7" s="6">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3">
+        <v>1</v>
+      </c>
+      <c r="I7" s="12">
+        <v>1</v>
+      </c>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4">
-        <v>1</v>
-      </c>
-      <c r="F8" s="8">
-        <v>1</v>
-      </c>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4">
-        <v>1</v>
-      </c>
-      <c r="I8" s="16">
-        <v>1</v>
-      </c>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="6">
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3">
+        <v>1</v>
+      </c>
+      <c r="F8" s="6">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3">
+        <v>1</v>
+      </c>
+      <c r="I8" s="12">
+        <v>1</v>
+      </c>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:26" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4">
-        <v>1</v>
-      </c>
-      <c r="F9" s="8">
-        <v>1</v>
-      </c>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4">
-        <v>1</v>
-      </c>
-      <c r="I9" s="16">
-        <v>1</v>
-      </c>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="6">
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3">
+        <v>1</v>
+      </c>
+      <c r="F9" s="6">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3">
+        <v>1</v>
+      </c>
+      <c r="I9" s="12">
+        <v>1</v>
+      </c>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4">
-        <v>1</v>
-      </c>
-      <c r="F10" s="8">
-        <v>1</v>
-      </c>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4">
-        <v>1</v>
-      </c>
-      <c r="I10" s="16">
-        <v>1</v>
-      </c>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="6">
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3">
+        <v>1</v>
+      </c>
+      <c r="F10" s="6">
+        <v>1</v>
+      </c>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3">
+        <v>1</v>
+      </c>
+      <c r="I10" s="12">
+        <v>1</v>
+      </c>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:26" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4">
-        <v>1</v>
-      </c>
-      <c r="F11" s="8">
-        <v>1</v>
-      </c>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4">
-        <v>1</v>
-      </c>
-      <c r="I11" s="16">
-        <v>1</v>
-      </c>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="6">
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3">
+        <v>1</v>
+      </c>
+      <c r="F11" s="6">
+        <v>1</v>
+      </c>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3">
+        <v>1</v>
+      </c>
+      <c r="I11" s="12">
+        <v>1</v>
+      </c>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4">
-        <v>1</v>
-      </c>
-      <c r="F12" s="8">
-        <v>1</v>
-      </c>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4">
-        <v>1</v>
-      </c>
-      <c r="I12" s="16">
-        <v>1</v>
-      </c>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="6">
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3">
+        <v>1</v>
+      </c>
+      <c r="F12" s="6">
+        <v>1</v>
+      </c>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3">
+        <v>1</v>
+      </c>
+      <c r="I12" s="12">
+        <v>1</v>
+      </c>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4">
-        <v>1</v>
-      </c>
-      <c r="F13" s="8">
-        <v>1</v>
-      </c>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4">
-        <v>1</v>
-      </c>
-      <c r="I13" s="16">
-        <v>1</v>
-      </c>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="6">
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3">
+        <v>1</v>
+      </c>
+      <c r="F13" s="6">
+        <v>1</v>
+      </c>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3">
+        <v>1</v>
+      </c>
+      <c r="I13" s="12">
+        <v>1</v>
+      </c>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:26" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4">
-        <v>1</v>
-      </c>
-      <c r="F14" s="8">
-        <v>1</v>
-      </c>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4">
-        <v>1</v>
-      </c>
-      <c r="I14" s="16">
-        <v>1</v>
-      </c>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="6">
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3">
+        <v>1</v>
+      </c>
+      <c r="F14" s="6">
+        <v>1</v>
+      </c>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3">
+        <v>1</v>
+      </c>
+      <c r="I14" s="12">
+        <v>1</v>
+      </c>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1"/>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16">
-        <v>1</v>
-      </c>
-      <c r="F15" s="16">
-        <v>1</v>
-      </c>
-      <c r="G15" s="15"/>
-      <c r="H15" s="16">
-        <v>1</v>
-      </c>
-      <c r="I15" s="16">
-        <v>1</v>
-      </c>
-      <c r="J15" s="16"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="6">
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12">
+        <v>1</v>
+      </c>
+      <c r="F15" s="12">
+        <v>1</v>
+      </c>
+      <c r="G15" s="11"/>
+      <c r="H15" s="12">
+        <v>1</v>
+      </c>
+      <c r="I15" s="12">
+        <v>1</v>
+      </c>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16">
-        <v>1</v>
-      </c>
-      <c r="F16" s="16">
-        <v>1</v>
-      </c>
-      <c r="G16" s="15"/>
-      <c r="H16" s="16">
-        <v>1</v>
-      </c>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="6">
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12">
+        <v>1</v>
+      </c>
+      <c r="F16" s="12">
+        <v>1</v>
+      </c>
+      <c r="G16" s="11"/>
+      <c r="H16" s="12">
+        <v>1</v>
+      </c>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -16183,29 +16107,29 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16">
-        <v>1</v>
-      </c>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="16">
-        <v>1</v>
-      </c>
-      <c r="K17" s="16">
-        <v>1</v>
-      </c>
-      <c r="L17" s="16">
-        <v>1</v>
-      </c>
-      <c r="M17" s="16"/>
-      <c r="N17" s="6">
+      <c r="B17" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12">
+        <v>1</v>
+      </c>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="12">
+        <v>1</v>
+      </c>
+      <c r="K17" s="12">
+        <v>1</v>
+      </c>
+      <c r="L17" s="12">
+        <v>1</v>
+      </c>
+      <c r="M17" s="12"/>
+      <c r="N17" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -16214,31 +16138,31 @@
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="16">
-        <v>1</v>
-      </c>
-      <c r="D18" s="16">
-        <v>1</v>
-      </c>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="16">
-        <v>1</v>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16">
-        <v>1</v>
-      </c>
-      <c r="M18" s="16">
-        <v>1</v>
-      </c>
-      <c r="N18" s="6">
+      <c r="B18" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="12">
+        <v>1</v>
+      </c>
+      <c r="D18" s="12">
+        <v>1</v>
+      </c>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="12">
+        <v>1</v>
+      </c>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12">
+        <v>1</v>
+      </c>
+      <c r="M18" s="12">
+        <v>1</v>
+      </c>
+      <c r="N18" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -16247,31 +16171,31 @@
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" s="16">
-        <v>1</v>
-      </c>
-      <c r="D19" s="16">
-        <v>1</v>
-      </c>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="16">
-        <v>1</v>
-      </c>
-      <c r="K19" s="16">
-        <v>1</v>
-      </c>
-      <c r="L19" s="16">
-        <v>1</v>
-      </c>
-      <c r="M19" s="15"/>
-      <c r="N19" s="6">
+      <c r="B19" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="12">
+        <v>1</v>
+      </c>
+      <c r="D19" s="12">
+        <v>1</v>
+      </c>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="12">
+        <v>1</v>
+      </c>
+      <c r="K19" s="12">
+        <v>1</v>
+      </c>
+      <c r="L19" s="12">
+        <v>1</v>
+      </c>
+      <c r="M19" s="11"/>
+      <c r="N19" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -16280,27 +16204,27 @@
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="16">
-        <v>1</v>
-      </c>
-      <c r="D20" s="16">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="16">
-        <v>1</v>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="6">
+      <c r="B20" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="12">
+        <v>1</v>
+      </c>
+      <c r="D20" s="12">
+        <v>1</v>
+      </c>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="12">
+        <v>1</v>
+      </c>
+      <c r="K20" s="12"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -16309,29 +16233,29 @@
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" s="16">
-        <v>1</v>
-      </c>
-      <c r="D21" s="16">
-        <v>1</v>
-      </c>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="16">
-        <v>1</v>
-      </c>
-      <c r="K21" s="16">
-        <v>1</v>
-      </c>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="6">
+      <c r="B21" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="12">
+        <v>1</v>
+      </c>
+      <c r="D21" s="12">
+        <v>1</v>
+      </c>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="12">
+        <v>1</v>
+      </c>
+      <c r="K21" s="12">
+        <v>1</v>
+      </c>
+      <c r="L21" s="12"/>
+      <c r="M21" s="12"/>
+      <c r="N21" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -16340,29 +16264,29 @@
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" s="16">
-        <v>1</v>
-      </c>
-      <c r="D22" s="16">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
-      <c r="J22" s="15"/>
-      <c r="K22" s="16">
-        <v>1</v>
-      </c>
-      <c r="L22" s="16">
-        <v>1</v>
-      </c>
-      <c r="M22" s="15"/>
-      <c r="N22" s="6">
+      <c r="B22" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="12">
+        <v>1</v>
+      </c>
+      <c r="D22" s="12">
+        <v>1</v>
+      </c>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="12">
+        <v>1</v>
+      </c>
+      <c r="L22" s="12">
+        <v>1</v>
+      </c>
+      <c r="M22" s="11"/>
+      <c r="N22" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -16371,29 +16295,29 @@
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" s="16">
-        <v>1</v>
-      </c>
-      <c r="D23" s="16">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="16">
-        <v>1</v>
-      </c>
-      <c r="K23" s="16">
-        <v>1</v>
-      </c>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="6">
+      <c r="B23" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="12">
+        <v>1</v>
+      </c>
+      <c r="D23" s="12">
+        <v>1</v>
+      </c>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="12">
+        <v>1</v>
+      </c>
+      <c r="K23" s="12">
+        <v>1</v>
+      </c>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -16402,29 +16326,29 @@
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" s="16">
-        <v>1</v>
-      </c>
-      <c r="D24" s="16">
-        <v>1</v>
-      </c>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="18">
-        <v>1</v>
-      </c>
-      <c r="K24" s="18">
-        <v>1</v>
-      </c>
-      <c r="L24" s="17"/>
-      <c r="M24" s="17"/>
-      <c r="N24" s="6">
+      <c r="B24" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="12">
+        <v>1</v>
+      </c>
+      <c r="D24" s="12">
+        <v>1</v>
+      </c>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="14">
+        <v>1</v>
+      </c>
+      <c r="K24" s="14">
+        <v>1</v>
+      </c>
+      <c r="L24" s="13"/>
+      <c r="M24" s="13"/>
+      <c r="N24" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -16433,31 +16357,31 @@
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25" s="16">
-        <v>1</v>
-      </c>
-      <c r="D25" s="16">
-        <v>1</v>
-      </c>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="16">
-        <v>1</v>
-      </c>
-      <c r="K25" s="16">
-        <v>1</v>
-      </c>
-      <c r="L25" s="16">
-        <v>1</v>
-      </c>
-      <c r="M25" s="15"/>
-      <c r="N25" s="6">
+      <c r="B25" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="12">
+        <v>1</v>
+      </c>
+      <c r="D25" s="12">
+        <v>1</v>
+      </c>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="12">
+        <v>1</v>
+      </c>
+      <c r="K25" s="12">
+        <v>1</v>
+      </c>
+      <c r="L25" s="12">
+        <v>1</v>
+      </c>
+      <c r="M25" s="11"/>
+      <c r="N25" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -16466,31 +16390,31 @@
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" s="16">
-        <v>1</v>
-      </c>
-      <c r="D26" s="16">
-        <v>1</v>
-      </c>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="16">
-        <v>1</v>
-      </c>
-      <c r="K26" s="16">
-        <v>1</v>
-      </c>
-      <c r="L26" s="16">
-        <v>1</v>
-      </c>
-      <c r="M26" s="15"/>
-      <c r="N26" s="6">
+      <c r="B26" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" s="12">
+        <v>1</v>
+      </c>
+      <c r="D26" s="12">
+        <v>1</v>
+      </c>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="12">
+        <v>1</v>
+      </c>
+      <c r="K26" s="12">
+        <v>1</v>
+      </c>
+      <c r="L26" s="12">
+        <v>1</v>
+      </c>
+      <c r="M26" s="11"/>
+      <c r="N26" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -16499,31 +16423,31 @@
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" s="16">
-        <v>1</v>
-      </c>
-      <c r="D27" s="16">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="16">
-        <v>1</v>
-      </c>
-      <c r="K27" s="16">
-        <v>1</v>
-      </c>
-      <c r="L27" s="16">
-        <v>1</v>
-      </c>
-      <c r="M27" s="15"/>
-      <c r="N27" s="6">
+      <c r="B27" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="12">
+        <v>1</v>
+      </c>
+      <c r="D27" s="12">
+        <v>1</v>
+      </c>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="12">
+        <v>1</v>
+      </c>
+      <c r="K27" s="12">
+        <v>1</v>
+      </c>
+      <c r="L27" s="12">
+        <v>1</v>
+      </c>
+      <c r="M27" s="11"/>
+      <c r="N27" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -16532,27 +16456,27 @@
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C28" s="15"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
-      <c r="J28" s="15"/>
-      <c r="K28" s="16">
-        <v>1</v>
-      </c>
-      <c r="L28" s="16">
-        <v>1</v>
-      </c>
-      <c r="M28" s="16">
-        <v>1</v>
-      </c>
-      <c r="N28" s="6">
+      <c r="B28" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" s="11"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="12">
+        <v>1</v>
+      </c>
+      <c r="L28" s="12">
+        <v>1</v>
+      </c>
+      <c r="M28" s="12">
+        <v>1</v>
+      </c>
+      <c r="N28" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -16561,31 +16485,31 @@
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C29" s="16">
-        <v>1</v>
-      </c>
-      <c r="D29" s="16">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
-      <c r="J29" s="16">
-        <v>1</v>
-      </c>
-      <c r="K29" s="16">
-        <v>1</v>
-      </c>
-      <c r="L29" s="16">
-        <v>1</v>
-      </c>
-      <c r="M29" s="15"/>
-      <c r="N29" s="6">
+      <c r="B29" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" s="12">
+        <v>1</v>
+      </c>
+      <c r="D29" s="12">
+        <v>1</v>
+      </c>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="12">
+        <v>1</v>
+      </c>
+      <c r="K29" s="12">
+        <v>1</v>
+      </c>
+      <c r="L29" s="12">
+        <v>1</v>
+      </c>
+      <c r="M29" s="11"/>
+      <c r="N29" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -16594,31 +16518,31 @@
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C30" s="16">
-        <v>1</v>
-      </c>
-      <c r="D30" s="16">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="16">
-        <v>1</v>
-      </c>
-      <c r="K30" s="16">
-        <v>1</v>
-      </c>
-      <c r="L30" s="16">
-        <v>1</v>
-      </c>
-      <c r="M30" s="15"/>
-      <c r="N30" s="6">
+      <c r="B30" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="12">
+        <v>1</v>
+      </c>
+      <c r="D30" s="12">
+        <v>1</v>
+      </c>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="12">
+        <v>1</v>
+      </c>
+      <c r="K30" s="12">
+        <v>1</v>
+      </c>
+      <c r="L30" s="12">
+        <v>1</v>
+      </c>
+      <c r="M30" s="11"/>
+      <c r="N30" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -16627,31 +16551,31 @@
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="16">
-        <v>1</v>
-      </c>
-      <c r="K31" s="16">
-        <v>1</v>
-      </c>
-      <c r="L31" s="16">
-        <v>1</v>
-      </c>
-      <c r="M31" s="16">
-        <v>1</v>
-      </c>
-      <c r="N31" s="6">
+      <c r="B31" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12">
+        <v>1</v>
+      </c>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="12">
+        <v>1</v>
+      </c>
+      <c r="K31" s="12">
+        <v>1</v>
+      </c>
+      <c r="L31" s="12">
+        <v>1</v>
+      </c>
+      <c r="M31" s="12">
+        <v>1</v>
+      </c>
+      <c r="N31" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -16660,29 +16584,29 @@
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C32" s="16">
-        <v>1</v>
-      </c>
-      <c r="D32" s="16"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="16">
-        <v>1</v>
-      </c>
-      <c r="K32" s="16">
-        <v>1</v>
-      </c>
-      <c r="L32" s="16">
-        <v>1</v>
-      </c>
-      <c r="M32" s="16"/>
-      <c r="N32" s="6">
+      <c r="B32" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" s="12">
+        <v>1</v>
+      </c>
+      <c r="D32" s="12"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="12">
+        <v>1</v>
+      </c>
+      <c r="K32" s="12">
+        <v>1</v>
+      </c>
+      <c r="L32" s="12">
+        <v>1</v>
+      </c>
+      <c r="M32" s="12"/>
+      <c r="N32" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -16691,29 +16615,29 @@
       <c r="A33" s="1">
         <v>31</v>
       </c>
-      <c r="B33" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C33" s="16">
-        <v>1</v>
-      </c>
-      <c r="D33" s="16">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="15"/>
-      <c r="J33" s="16">
-        <v>1</v>
-      </c>
-      <c r="K33" s="16">
-        <v>1</v>
-      </c>
-      <c r="L33" s="16"/>
-      <c r="M33" s="15"/>
-      <c r="N33" s="6">
+      <c r="B33" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" s="12">
+        <v>1</v>
+      </c>
+      <c r="D33" s="12">
+        <v>1</v>
+      </c>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="12">
+        <v>1</v>
+      </c>
+      <c r="K33" s="12">
+        <v>1</v>
+      </c>
+      <c r="L33" s="12"/>
+      <c r="M33" s="11"/>
+      <c r="N33" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -16721,49 +16645,49 @@
     <row r="34" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C34" s="6">
+        <v>27</v>
+      </c>
+      <c r="C34" s="5">
         <f t="shared" ref="C34:M34" si="1">SUM(C3:C33)</f>
         <v>14</v>
       </c>
-      <c r="D34" s="6">
+      <c r="D34" s="5">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="E34" s="6">
+      <c r="E34" s="5">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="F34" s="6">
+      <c r="F34" s="5">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="G34" s="6">
+      <c r="G34" s="5">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H34" s="6">
+      <c r="H34" s="5">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="I34" s="6">
+      <c r="I34" s="5">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="J34" s="6">
+      <c r="J34" s="5">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="K34" s="6">
+      <c r="K34" s="5">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="L34" s="6">
+      <c r="L34" s="5">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="M34" s="6">
+      <c r="M34" s="5">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
@@ -20644,7 +20568,7 @@
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="2" width="26.09765625" customWidth="1"/>
+    <col min="2" max="2" width="42.296875" customWidth="1"/>
     <col min="3" max="8" width="10.59765625" customWidth="1"/>
     <col min="9" max="9" width="9" customWidth="1"/>
     <col min="10" max="13" width="10.59765625" customWidth="1"/>
@@ -20706,7 +20630,7 @@
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>1</v>
@@ -20752,460 +20676,460 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
-    <row r="3" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="4">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1</v>
-      </c>
-      <c r="E3" s="4">
-        <v>1</v>
-      </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4">
-        <v>1</v>
-      </c>
-      <c r="H3" s="4">
-        <v>1</v>
-      </c>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="6">
+      <c r="C3" s="3">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3">
+        <v>1</v>
+      </c>
+      <c r="H3" s="3">
+        <v>1</v>
+      </c>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="5">
         <f>SUM(C3:M3)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="4">
-        <v>1</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1</v>
-      </c>
-      <c r="E4" s="4">
-        <v>1</v>
-      </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4">
-        <v>1</v>
-      </c>
-      <c r="H4" s="4">
-        <v>1</v>
-      </c>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="6">
+      <c r="C4" s="3">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3">
+        <v>1</v>
+      </c>
+      <c r="H4" s="3">
+        <v>1</v>
+      </c>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="5">
         <f t="shared" ref="N4:N33" si="0">SUM(C4:M4)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4">
-        <v>1</v>
-      </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4">
-        <v>1</v>
-      </c>
-      <c r="H5" s="4">
-        <v>1</v>
-      </c>
-      <c r="I5" s="16">
-        <v>1</v>
-      </c>
-      <c r="J5" s="16"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="6">
+      <c r="C5" s="6"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3">
+        <v>1</v>
+      </c>
+      <c r="H5" s="3">
+        <v>1</v>
+      </c>
+      <c r="I5" s="12">
+        <v>1</v>
+      </c>
+      <c r="J5" s="12"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="4">
-        <v>1</v>
-      </c>
-      <c r="D6" s="4">
-        <v>1</v>
-      </c>
-      <c r="E6" s="4">
-        <v>1</v>
-      </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4">
-        <v>1</v>
-      </c>
-      <c r="H6" s="4">
-        <v>1</v>
-      </c>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="6">
+      <c r="C6" s="3">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3">
+        <v>1</v>
+      </c>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="4">
-        <v>1</v>
-      </c>
-      <c r="D7" s="4">
-        <v>1</v>
-      </c>
-      <c r="E7" s="4">
-        <v>1</v>
-      </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4">
-        <v>1</v>
-      </c>
-      <c r="H7" s="4">
-        <v>1</v>
-      </c>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="6">
+      <c r="C7" s="3">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3">
+        <v>1</v>
+      </c>
+      <c r="H7" s="3">
+        <v>1</v>
+      </c>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="4">
-        <v>1</v>
-      </c>
-      <c r="D8" s="4">
-        <v>1</v>
-      </c>
-      <c r="E8" s="4">
-        <v>1</v>
-      </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4">
-        <v>1</v>
-      </c>
-      <c r="H8" s="4">
-        <v>1</v>
-      </c>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="6">
+      <c r="C8" s="3">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3">
+        <v>1</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1</v>
+      </c>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:26" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="4">
-        <v>1</v>
-      </c>
-      <c r="D9" s="4">
-        <v>1</v>
-      </c>
-      <c r="E9" s="4">
-        <v>1</v>
-      </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4">
-        <v>1</v>
-      </c>
-      <c r="I9" s="16">
-        <v>1</v>
-      </c>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="6">
+      <c r="C9" s="3">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3">
+        <v>1</v>
+      </c>
+      <c r="I9" s="12">
+        <v>1</v>
+      </c>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="4">
-        <v>1</v>
-      </c>
-      <c r="D10" s="4">
-        <v>1</v>
-      </c>
-      <c r="E10" s="4">
-        <v>1</v>
-      </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4">
-        <v>1</v>
-      </c>
-      <c r="I10" s="16">
-        <v>1</v>
-      </c>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="6">
+      <c r="C10" s="3">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3">
+        <v>1</v>
+      </c>
+      <c r="I10" s="12">
+        <v>1</v>
+      </c>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:26" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="4">
-        <v>1</v>
-      </c>
-      <c r="D11" s="4">
-        <v>1</v>
-      </c>
-      <c r="E11" s="4">
-        <v>1</v>
-      </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4">
-        <v>1</v>
-      </c>
-      <c r="H11" s="4">
-        <v>1</v>
-      </c>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="6">
+      <c r="C11" s="3">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3">
+        <v>1</v>
+      </c>
+      <c r="H11" s="3">
+        <v>1</v>
+      </c>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="4">
-        <v>1</v>
-      </c>
-      <c r="D12" s="4">
-        <v>1</v>
-      </c>
-      <c r="E12" s="4">
-        <v>1</v>
-      </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4">
-        <v>1</v>
-      </c>
-      <c r="H12" s="4">
-        <v>1</v>
-      </c>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="6">
+      <c r="C12" s="3">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3">
+        <v>1</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1</v>
+      </c>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="4">
-        <v>1</v>
-      </c>
-      <c r="D13" s="4">
-        <v>1</v>
-      </c>
-      <c r="E13" s="4">
-        <v>1</v>
-      </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4">
-        <v>1</v>
-      </c>
-      <c r="H13" s="4">
-        <v>1</v>
-      </c>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="6">
+      <c r="C13" s="3">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3">
+        <v>1</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3">
+        <v>1</v>
+      </c>
+      <c r="H13" s="3">
+        <v>1</v>
+      </c>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:26" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="4">
-        <v>1</v>
-      </c>
-      <c r="D14" s="4">
-        <v>1</v>
-      </c>
-      <c r="E14" s="4">
-        <v>1</v>
-      </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4">
-        <v>1</v>
-      </c>
-      <c r="H14" s="4">
-        <v>1</v>
-      </c>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="6">
+      <c r="C14" s="3">
+        <v>1</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3">
+        <v>1</v>
+      </c>
+      <c r="H14" s="3">
+        <v>1</v>
+      </c>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:26" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:26" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="4">
-        <v>1</v>
-      </c>
-      <c r="D15" s="4">
-        <v>1</v>
-      </c>
-      <c r="E15" s="4">
-        <v>1</v>
-      </c>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4">
-        <v>1</v>
-      </c>
-      <c r="H15" s="4"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="6">
+      <c r="C15" s="3">
+        <v>1</v>
+      </c>
+      <c r="D15" s="3">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3">
+        <v>1</v>
+      </c>
+      <c r="H15" s="3"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="16">
-        <v>1</v>
-      </c>
-      <c r="F16" s="16">
-        <v>1</v>
-      </c>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16">
-        <v>1</v>
-      </c>
-      <c r="I16" s="16">
-        <v>1</v>
-      </c>
-      <c r="J16" s="16">
-        <v>1</v>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="6">
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="12">
+        <v>1</v>
+      </c>
+      <c r="F16" s="12">
+        <v>1</v>
+      </c>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12">
+        <v>1</v>
+      </c>
+      <c r="I16" s="12">
+        <v>1</v>
+      </c>
+      <c r="J16" s="12">
+        <v>1</v>
+      </c>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -21214,27 +21138,27 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="16">
-        <v>1</v>
-      </c>
-      <c r="L17" s="16">
-        <v>1</v>
-      </c>
-      <c r="M17" s="16">
-        <v>1</v>
-      </c>
-      <c r="N17" s="6">
+      <c r="B17" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="12">
+        <v>1</v>
+      </c>
+      <c r="L17" s="12">
+        <v>1</v>
+      </c>
+      <c r="M17" s="12">
+        <v>1</v>
+      </c>
+      <c r="N17" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -21243,21 +21167,21 @@
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="6">
+      <c r="B18" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -21266,27 +21190,27 @@
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="16">
-        <v>1</v>
-      </c>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="16">
-        <v>1</v>
-      </c>
-      <c r="L19" s="16">
-        <v>1</v>
-      </c>
-      <c r="M19" s="15"/>
-      <c r="N19" s="6">
+      <c r="B19" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="12">
+        <v>1</v>
+      </c>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="12">
+        <v>1</v>
+      </c>
+      <c r="L19" s="12">
+        <v>1</v>
+      </c>
+      <c r="M19" s="11"/>
+      <c r="N19" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -21295,25 +21219,25 @@
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="16">
-        <v>1</v>
-      </c>
-      <c r="L20" s="16">
-        <v>1</v>
-      </c>
-      <c r="M20" s="15"/>
-      <c r="N20" s="6">
+      <c r="B20" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="12">
+        <v>1</v>
+      </c>
+      <c r="L20" s="12">
+        <v>1</v>
+      </c>
+      <c r="M20" s="11"/>
+      <c r="N20" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -21322,27 +21246,27 @@
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" s="16"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="16">
-        <v>1</v>
-      </c>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="16">
-        <v>1</v>
-      </c>
-      <c r="L21" s="16">
-        <v>1</v>
-      </c>
-      <c r="M21" s="16"/>
-      <c r="N21" s="6">
+      <c r="B21" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="12"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="12">
+        <v>1</v>
+      </c>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="12">
+        <v>1</v>
+      </c>
+      <c r="L21" s="12">
+        <v>1</v>
+      </c>
+      <c r="M21" s="12"/>
+      <c r="N21" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -21351,29 +21275,29 @@
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="16">
-        <v>1</v>
-      </c>
-      <c r="J22" s="16">
-        <v>1</v>
-      </c>
-      <c r="K22" s="16">
-        <v>1</v>
-      </c>
-      <c r="L22" s="16">
-        <v>1</v>
-      </c>
-      <c r="M22" s="15"/>
-      <c r="N22" s="6">
+      <c r="B22" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="12">
+        <v>1</v>
+      </c>
+      <c r="J22" s="12">
+        <v>1</v>
+      </c>
+      <c r="K22" s="12">
+        <v>1</v>
+      </c>
+      <c r="L22" s="12">
+        <v>1</v>
+      </c>
+      <c r="M22" s="11"/>
+      <c r="N22" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -21382,29 +21306,29 @@
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" s="16">
-        <v>1</v>
-      </c>
-      <c r="D23" s="16">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
-      <c r="K23" s="16">
-        <v>1</v>
-      </c>
-      <c r="L23" s="16">
-        <v>1</v>
-      </c>
-      <c r="M23" s="15"/>
-      <c r="N23" s="6">
+      <c r="B23" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="12">
+        <v>1</v>
+      </c>
+      <c r="D23" s="12">
+        <v>1</v>
+      </c>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12">
+        <v>1</v>
+      </c>
+      <c r="L23" s="12">
+        <v>1</v>
+      </c>
+      <c r="M23" s="11"/>
+      <c r="N23" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -21413,29 +21337,29 @@
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" s="16">
-        <v>1</v>
-      </c>
-      <c r="D24" s="16">
-        <v>1</v>
-      </c>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="18">
-        <v>1</v>
-      </c>
-      <c r="L24" s="18">
-        <v>1</v>
-      </c>
-      <c r="M24" s="17"/>
-      <c r="N24" s="6">
+      <c r="B24" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="12">
+        <v>1</v>
+      </c>
+      <c r="D24" s="12">
+        <v>1</v>
+      </c>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="14">
+        <v>1</v>
+      </c>
+      <c r="L24" s="14">
+        <v>1</v>
+      </c>
+      <c r="M24" s="13"/>
+      <c r="N24" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -21444,25 +21368,25 @@
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="16">
-        <v>1</v>
-      </c>
-      <c r="L25" s="16">
-        <v>1</v>
-      </c>
-      <c r="M25" s="15"/>
-      <c r="N25" s="6">
+      <c r="B25" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="12">
+        <v>1</v>
+      </c>
+      <c r="L25" s="12">
+        <v>1</v>
+      </c>
+      <c r="M25" s="11"/>
+      <c r="N25" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -21471,25 +21395,25 @@
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="16"/>
-      <c r="K26" s="16">
-        <v>1</v>
-      </c>
-      <c r="L26" s="16">
-        <v>1</v>
-      </c>
-      <c r="M26" s="15"/>
-      <c r="N26" s="6">
+      <c r="B26" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12">
+        <v>1</v>
+      </c>
+      <c r="L26" s="12">
+        <v>1</v>
+      </c>
+      <c r="M26" s="11"/>
+      <c r="N26" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -21498,25 +21422,25 @@
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="16"/>
-      <c r="K27" s="16">
-        <v>1</v>
-      </c>
-      <c r="L27" s="16">
-        <v>1</v>
-      </c>
-      <c r="M27" s="15"/>
-      <c r="N27" s="6">
+      <c r="B27" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12">
+        <v>1</v>
+      </c>
+      <c r="L27" s="12">
+        <v>1</v>
+      </c>
+      <c r="M27" s="11"/>
+      <c r="N27" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -21525,29 +21449,29 @@
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C28" s="16"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
-      <c r="J28" s="16">
-        <v>1</v>
-      </c>
-      <c r="K28" s="16">
-        <v>1</v>
-      </c>
-      <c r="L28" s="16">
-        <v>1</v>
-      </c>
-      <c r="M28" s="16">
-        <v>1</v>
-      </c>
-      <c r="N28" s="6">
+      <c r="B28" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" s="12"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="12">
+        <v>1</v>
+      </c>
+      <c r="K28" s="12">
+        <v>1</v>
+      </c>
+      <c r="L28" s="12">
+        <v>1</v>
+      </c>
+      <c r="M28" s="12">
+        <v>1</v>
+      </c>
+      <c r="N28" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -21556,21 +21480,21 @@
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
-      <c r="J29" s="15"/>
-      <c r="K29" s="15"/>
-      <c r="L29" s="15"/>
-      <c r="M29" s="15"/>
-      <c r="N29" s="6">
+      <c r="B29" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -21579,21 +21503,21 @@
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="15"/>
-      <c r="L30" s="15"/>
-      <c r="M30" s="15"/>
-      <c r="N30" s="6">
+      <c r="B30" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+      <c r="N30" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -21602,29 +21526,29 @@
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="16">
-        <v>1</v>
-      </c>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="16"/>
-      <c r="K31" s="16">
-        <v>1</v>
-      </c>
-      <c r="L31" s="16">
-        <v>1</v>
-      </c>
-      <c r="M31" s="16">
-        <v>1</v>
-      </c>
-      <c r="N31" s="6">
+      <c r="B31" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="12">
+        <v>1</v>
+      </c>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="12">
+        <v>1</v>
+      </c>
+      <c r="L31" s="12">
+        <v>1</v>
+      </c>
+      <c r="M31" s="12">
+        <v>1</v>
+      </c>
+      <c r="N31" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -21633,31 +21557,31 @@
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C32" s="16">
-        <v>1</v>
-      </c>
-      <c r="D32" s="16">
-        <v>1</v>
-      </c>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="15"/>
-      <c r="K32" s="16">
-        <v>1</v>
-      </c>
-      <c r="L32" s="16">
-        <v>1</v>
-      </c>
-      <c r="M32" s="16">
-        <v>1</v>
-      </c>
-      <c r="N32" s="6">
+      <c r="B32" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" s="12">
+        <v>1</v>
+      </c>
+      <c r="D32" s="12">
+        <v>1</v>
+      </c>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="12">
+        <v>1</v>
+      </c>
+      <c r="L32" s="12">
+        <v>1</v>
+      </c>
+      <c r="M32" s="12">
+        <v>1</v>
+      </c>
+      <c r="N32" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -21666,25 +21590,25 @@
       <c r="A33" s="1">
         <v>31</v>
       </c>
-      <c r="B33" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="15"/>
-      <c r="J33" s="15"/>
-      <c r="K33" s="16">
-        <v>1</v>
-      </c>
-      <c r="L33" s="16">
-        <v>1</v>
-      </c>
-      <c r="M33" s="15"/>
-      <c r="N33" s="6">
+      <c r="B33" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="12">
+        <v>1</v>
+      </c>
+      <c r="L33" s="12">
+        <v>1</v>
+      </c>
+      <c r="M33" s="11"/>
+      <c r="N33" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -21692,49 +21616,49 @@
     <row r="34" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C34" s="6">
+        <v>27</v>
+      </c>
+      <c r="C34" s="5">
         <f t="shared" ref="C34:M34" si="1">SUM(C3:C33)</f>
         <v>15</v>
       </c>
-      <c r="D34" s="6">
+      <c r="D34" s="5">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="E34" s="6">
+      <c r="E34" s="5">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="F34" s="6">
+      <c r="F34" s="5">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="G34" s="6">
+      <c r="G34" s="5">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="H34" s="6">
+      <c r="H34" s="5">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="I34" s="6">
+      <c r="I34" s="5">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="J34" s="6">
+      <c r="J34" s="5">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K34" s="6">
+      <c r="K34" s="5">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="L34" s="6">
+      <c r="L34" s="5">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="M34" s="6">
+      <c r="M34" s="5">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -25620,21 +25544,21 @@
     <col min="2" max="2" width="26.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="19"/>
-      <c r="C1" s="14" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="15"/>
+      <c r="C1" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="5">
         <f>Monday!N3+Tuesday!N3+Wednesday!N3+Thursday!N3+Friday!N3</f>
         <v>23</v>
       </c>
@@ -25643,10 +25567,10 @@
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <f>Monday!N4+Tuesday!N4+Wednesday!N4+Thursday!N4+Friday!N4</f>
         <v>23</v>
       </c>
@@ -25655,10 +25579,10 @@
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <f>Monday!N5+Tuesday!N5+Wednesday!N5+Thursday!N5+Friday!N5</f>
         <v>23</v>
       </c>
@@ -25667,10 +25591,10 @@
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <f>Monday!N6+Tuesday!N6+Wednesday!N6+Thursday!N6+Friday!N6</f>
         <v>23</v>
       </c>
@@ -25679,10 +25603,10 @@
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="5">
         <f>Monday!N7+Tuesday!N7+Wednesday!N7+Thursday!N7+Friday!N7</f>
         <v>23</v>
       </c>
@@ -25691,10 +25615,10 @@
       <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <f>Monday!N8+Tuesday!N8+Wednesday!N8+Thursday!N8+Friday!N8</f>
         <v>23</v>
       </c>
@@ -25703,10 +25627,10 @@
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <f>Monday!N9+Tuesday!N9+Wednesday!N9+Thursday!N9+Friday!N9</f>
         <v>23</v>
       </c>
@@ -25715,10 +25639,10 @@
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="5">
         <f>Monday!N10+Tuesday!N10+Wednesday!N10+Thursday!N10+Friday!N10</f>
         <v>23</v>
       </c>
@@ -25727,10 +25651,10 @@
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="5">
         <f>Monday!N11+Tuesday!N11+Wednesday!N11+Thursday!N11+Friday!N11</f>
         <v>23</v>
       </c>
@@ -25739,10 +25663,10 @@
       <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="5">
         <f>Monday!N12+Tuesday!N12+Wednesday!N12+Thursday!N12+Friday!N12</f>
         <v>23</v>
       </c>
@@ -25751,10 +25675,10 @@
       <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="5">
         <f>Monday!N13+Tuesday!N13+Wednesday!N13+Thursday!N13+Friday!N13</f>
         <v>23</v>
       </c>
@@ -25763,10 +25687,10 @@
       <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="5">
         <f>Monday!N14+Tuesday!N14+Wednesday!N14+Thursday!N14+Friday!N14</f>
         <v>23</v>
       </c>
@@ -25775,10 +25699,10 @@
       <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="5">
         <f>Monday!N15+Tuesday!N15+Wednesday!N15+Thursday!N15+Friday!N15</f>
         <v>22</v>
       </c>
@@ -25787,10 +25711,10 @@
       <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="5">
         <f>Monday!N16+Tuesday!N16+Wednesday!N16+Thursday!N16+Friday!N16</f>
         <v>23</v>
       </c>
@@ -25799,10 +25723,10 @@
       <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" s="6">
+      <c r="B16" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="5">
         <f>Monday!N17+Tuesday!N17+Wednesday!N17+Thursday!N17+Friday!N17</f>
         <v>16</v>
       </c>
@@ -25811,10 +25735,10 @@
       <c r="A17" s="2">
         <v>16</v>
       </c>
-      <c r="B17" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="6">
+      <c r="B17" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="5">
         <f>Monday!N18+Tuesday!N18+Wednesday!N18+Thursday!N18+Friday!N18</f>
         <v>17</v>
       </c>
@@ -25823,10 +25747,10 @@
       <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="B18" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="C18" s="6">
+      <c r="B18" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="5">
         <f>Monday!N19+Tuesday!N19+Wednesday!N19+Thursday!N19+Friday!N19</f>
         <v>17</v>
       </c>
@@ -25835,10 +25759,10 @@
       <c r="A19" s="2">
         <v>18</v>
       </c>
-      <c r="B19" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="6">
+      <c r="B19" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="5">
         <f>Monday!N20+Tuesday!N20+Wednesday!N20+Thursday!N20+Friday!N20</f>
         <v>17</v>
       </c>
@@ -25847,10 +25771,10 @@
       <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="B20" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="C20" s="6">
+      <c r="B20" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="5">
         <f>Monday!N21+Tuesday!N21+Wednesday!N21+Thursday!N21+Friday!N21</f>
         <v>17</v>
       </c>
@@ -25859,10 +25783,10 @@
       <c r="A21" s="2">
         <v>20</v>
       </c>
-      <c r="B21" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" s="6">
+      <c r="B21" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="5">
         <f>Monday!N22+Tuesday!N22+Wednesday!N22+Thursday!N22+Friday!N22</f>
         <v>17</v>
       </c>
@@ -25871,10 +25795,10 @@
       <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="B22" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="C22" s="6">
+      <c r="B22" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="5">
         <f>Monday!N23+Tuesday!N23+Wednesday!N23+Thursday!N23+Friday!N23</f>
         <v>17</v>
       </c>
@@ -25883,10 +25807,10 @@
       <c r="A23" s="2">
         <v>22</v>
       </c>
-      <c r="B23" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="C23" s="6">
+      <c r="B23" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="5">
         <f>Monday!N24+Tuesday!N24+Wednesday!N24+Thursday!N24+Friday!N24</f>
         <v>17</v>
       </c>
@@ -25895,10 +25819,10 @@
       <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="B24" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" s="6">
+      <c r="B24" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="5">
         <f>Monday!N25+Tuesday!N25+Wednesday!N25+Thursday!N25+Friday!N25</f>
         <v>17</v>
       </c>
@@ -25907,10 +25831,10 @@
       <c r="A25" s="2">
         <v>24</v>
       </c>
-      <c r="B25" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="C25" s="6">
+      <c r="B25" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" s="5">
         <f>Monday!N26+Tuesday!N26+Wednesday!N26+Thursday!N26+Friday!N26</f>
         <v>17</v>
       </c>
@@ -25919,10 +25843,10 @@
       <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="B26" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="C26" s="6">
+      <c r="B26" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="5">
         <f>Monday!N27+Tuesday!N27+Wednesday!N27+Thursday!N27+Friday!N27</f>
         <v>17</v>
       </c>
@@ -25931,10 +25855,10 @@
       <c r="A27" s="2">
         <v>26</v>
       </c>
-      <c r="B27" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="C27" s="6">
+      <c r="B27" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="5">
         <f>Monday!N28+Tuesday!N28+Wednesday!N28+Thursday!N28+Friday!N28</f>
         <v>17</v>
       </c>
@@ -25943,10 +25867,10 @@
       <c r="A28" s="1">
         <v>27</v>
       </c>
-      <c r="B28" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="C28" s="6">
+      <c r="B28" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" s="5">
         <f>Monday!N29+Tuesday!N29+Wednesday!N29+Thursday!N29+Friday!N29</f>
         <v>17</v>
       </c>
@@ -25955,10 +25879,10 @@
       <c r="A29" s="2">
         <v>28</v>
       </c>
-      <c r="B29" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C29" s="6">
+      <c r="B29" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29" s="5">
         <f>Monday!N30+Tuesday!N30+Wednesday!N30+Thursday!N30+Friday!N30</f>
         <v>17</v>
       </c>
@@ -25967,22 +25891,22 @@
       <c r="A30" s="1">
         <v>29</v>
       </c>
-      <c r="B30" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="C30" s="6">
+      <c r="B30" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" s="5">
         <f>Monday!N31+Tuesday!N31+Wednesday!N31+Thursday!N31+Friday!N31</f>
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>30</v>
       </c>
-      <c r="B31" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="C31" s="6">
+      <c r="B31" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" s="5">
         <f>Monday!N32+Tuesday!N32+Wednesday!N32+Thursday!N32+Friday!N32</f>
         <v>17</v>
       </c>
@@ -25991,10 +25915,10 @@
       <c r="A32" s="1">
         <v>31</v>
       </c>
-      <c r="B32" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="C32" s="6">
+      <c r="B32" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" s="5">
         <f>Monday!N33+Tuesday!N33+Wednesday!N33+Thursday!N33+Friday!N33</f>
         <v>17</v>
       </c>
